--- a/Config/MonsterGroupConfig.xlsx
+++ b/Config/MonsterGroupConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="16650" windowHeight="14775"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -1224,7 +1224,7 @@
         <v>1001</v>
       </c>
       <c r="D7" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
@@ -1239,7 +1239,7 @@
         <v>1001</v>
       </c>
       <c r="D9" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
@@ -1254,7 +1254,7 @@
         <v>1001</v>
       </c>
       <c r="D11" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
@@ -1266,10 +1266,10 @@
         <v>12</v>
       </c>
       <c r="C12" s="2">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="D12" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
@@ -1284,7 +1284,7 @@
         <v>1001</v>
       </c>
       <c r="D14" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
@@ -1296,10 +1296,10 @@
         <v>14</v>
       </c>
       <c r="C15" s="2">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="D15" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
@@ -1314,7 +1314,7 @@
         <v>1001</v>
       </c>
       <c r="D17" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
@@ -1326,10 +1326,10 @@
         <v>16</v>
       </c>
       <c r="C18" s="2">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="D18" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
@@ -1344,7 +1344,7 @@
         <v>1001</v>
       </c>
       <c r="D20" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
@@ -1356,10 +1356,10 @@
         <v>18</v>
       </c>
       <c r="C21" s="2">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="D21" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
@@ -1371,10 +1371,10 @@
         <v>19</v>
       </c>
       <c r="C22" s="2">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="D22" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
@@ -1389,7 +1389,7 @@
         <v>1001</v>
       </c>
       <c r="D24" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
@@ -1401,10 +1401,10 @@
         <v>21</v>
       </c>
       <c r="C25" s="2">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="D25" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
@@ -1416,10 +1416,10 @@
         <v>22</v>
       </c>
       <c r="C26" s="2">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="D26" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
@@ -1434,7 +1434,7 @@
         <v>1001</v>
       </c>
       <c r="D28" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
@@ -1446,10 +1446,10 @@
         <v>24</v>
       </c>
       <c r="C29" s="2">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="D29" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
@@ -1461,10 +1461,10 @@
         <v>25</v>
       </c>
       <c r="C30" s="2">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="D30" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
@@ -1494,7 +1494,7 @@
         <v>1001</v>
       </c>
       <c r="D33" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
@@ -1506,10 +1506,10 @@
         <v>28</v>
       </c>
       <c r="C34" s="2">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="D34" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" s="2"/>

--- a/Config/MonsterGroupConfig.xlsx
+++ b/Config/MonsterGroupConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="16650" windowHeight="14775"/>
+    <workbookView windowWidth="15420" windowHeight="14775"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -779,11 +779,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1221,10 +1224,10 @@
         <v>9</v>
       </c>
       <c r="C7" s="2">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="D7" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
@@ -1236,10 +1239,10 @@
         <v>10</v>
       </c>
       <c r="C9" s="2">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="D9" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
@@ -1251,10 +1254,10 @@
         <v>11</v>
       </c>
       <c r="C11" s="2">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="D11" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
@@ -1266,10 +1269,10 @@
         <v>12</v>
       </c>
       <c r="C12" s="2">
-        <v>1001</v>
+        <v>1005</v>
       </c>
       <c r="D12" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
@@ -1284,7 +1287,7 @@
         <v>1001</v>
       </c>
       <c r="D14" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
@@ -1296,10 +1299,10 @@
         <v>14</v>
       </c>
       <c r="C15" s="2">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="D15" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
@@ -1311,10 +1314,10 @@
         <v>15</v>
       </c>
       <c r="C17" s="2">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="D17" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
@@ -1326,10 +1329,10 @@
         <v>16</v>
       </c>
       <c r="C18" s="2">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="D18" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
@@ -1341,10 +1344,10 @@
         <v>17</v>
       </c>
       <c r="C20" s="2">
-        <v>1001</v>
+        <v>1005</v>
       </c>
       <c r="D20" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
@@ -1359,7 +1362,7 @@
         <v>1001</v>
       </c>
       <c r="D21" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
@@ -1371,10 +1374,10 @@
         <v>19</v>
       </c>
       <c r="C22" s="2">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="D22" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
@@ -1386,10 +1389,10 @@
         <v>20</v>
       </c>
       <c r="C24" s="2">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="D24" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
@@ -1401,10 +1404,10 @@
         <v>21</v>
       </c>
       <c r="C25" s="2">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="D25" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
@@ -1416,10 +1419,10 @@
         <v>22</v>
       </c>
       <c r="C26" s="2">
-        <v>1001</v>
+        <v>1005</v>
       </c>
       <c r="D26" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
@@ -1434,7 +1437,7 @@
         <v>1001</v>
       </c>
       <c r="D28" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
@@ -1446,10 +1449,10 @@
         <v>24</v>
       </c>
       <c r="C29" s="2">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="D29" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
@@ -1461,10 +1464,10 @@
         <v>25</v>
       </c>
       <c r="C30" s="2">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="D30" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
@@ -1475,11 +1478,11 @@
       <c r="B32" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C32" s="2">
-        <v>2001</v>
-      </c>
-      <c r="D32" s="2">
-        <v>1</v>
+      <c r="C32" s="3">
+        <v>1004</v>
+      </c>
+      <c r="D32" s="3">
+        <v>4</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
@@ -1491,10 +1494,10 @@
         <v>27</v>
       </c>
       <c r="C33" s="2">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="D33" s="2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
@@ -1505,11 +1508,11 @@
       <c r="B34" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C34" s="2">
-        <v>1001</v>
+      <c r="C34" s="3">
+        <v>1005</v>
       </c>
       <c r="D34" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" s="2"/>

--- a/Config/MonsterGroupConfig.xlsx
+++ b/Config/MonsterGroupConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="15420" windowHeight="14775"/>
+    <workbookView windowWidth="6855" windowHeight="14775"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="50">
   <si>
     <t>##var</t>
   </si>
@@ -153,6 +153,69 @@
   </si>
   <si>
     <t>10103</t>
+  </si>
+  <si>
+    <t>20011</t>
+  </si>
+  <si>
+    <t>20021</t>
+  </si>
+  <si>
+    <t>20031</t>
+  </si>
+  <si>
+    <t>20041</t>
+  </si>
+  <si>
+    <t>20042</t>
+  </si>
+  <si>
+    <t>20051</t>
+  </si>
+  <si>
+    <t>20052</t>
+  </si>
+  <si>
+    <t>20061</t>
+  </si>
+  <si>
+    <t>20062</t>
+  </si>
+  <si>
+    <t>20071</t>
+  </si>
+  <si>
+    <t>20072</t>
+  </si>
+  <si>
+    <t>20073</t>
+  </si>
+  <si>
+    <t>20081</t>
+  </si>
+  <si>
+    <t>20082</t>
+  </si>
+  <si>
+    <t>20083</t>
+  </si>
+  <si>
+    <t>20091</t>
+  </si>
+  <si>
+    <t>20092</t>
+  </si>
+  <si>
+    <t>20093</t>
+  </si>
+  <si>
+    <t>20101</t>
+  </si>
+  <si>
+    <t>20102</t>
+  </si>
+  <si>
+    <t>20103</t>
   </si>
 </sst>
 </file>
@@ -779,14 +842,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1140,7 +1200,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -1211,9 +1271,15 @@
     </row>
     <row r="6" customFormat="1" spans="1:7">
       <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
+      <c r="B6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="2">
+        <v>1002</v>
+      </c>
+      <c r="D6" s="2">
+        <v>1</v>
+      </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
@@ -1221,10 +1287,10 @@
     <row r="7" customFormat="1" spans="1:7">
       <c r="A7" s="1"/>
       <c r="B7" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C7" s="2">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="D7" s="2">
         <v>1</v>
@@ -1233,13 +1299,28 @@
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
     </row>
+    <row r="8" customFormat="1" spans="1:7">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="2">
+        <v>1004</v>
+      </c>
+      <c r="D8" s="2">
+        <v>1</v>
+      </c>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+    </row>
     <row r="9" customFormat="1" spans="1:7">
       <c r="A9" s="1"/>
       <c r="B9" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C9" s="2">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="D9" s="2">
         <v>1</v>
@@ -1248,16 +1329,31 @@
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
     </row>
+    <row r="10" customFormat="1" spans="1:7">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="2">
+        <v>1001</v>
+      </c>
+      <c r="D10" s="2">
+        <v>2</v>
+      </c>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+    </row>
     <row r="11" customFormat="1" spans="1:7">
       <c r="A11" s="1"/>
       <c r="B11" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C11" s="2">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="D11" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
@@ -1266,25 +1362,40 @@
     <row r="12" customFormat="1" spans="1:7">
       <c r="A12" s="1"/>
       <c r="B12" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C12" s="2">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="D12" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
     </row>
+    <row r="13" customFormat="1" spans="1:7">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="2">
+        <v>1004</v>
+      </c>
+      <c r="D13" s="2">
+        <v>2</v>
+      </c>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+    </row>
     <row r="14" customFormat="1" spans="1:7">
       <c r="A14" s="1"/>
       <c r="B14" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C14" s="2">
-        <v>1001</v>
+        <v>1005</v>
       </c>
       <c r="D14" s="2">
         <v>2</v>
@@ -1296,28 +1407,43 @@
     <row r="15" customFormat="1" spans="1:7">
       <c r="A15" s="1"/>
       <c r="B15" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C15" s="2">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="D15" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
     </row>
+    <row r="16" customFormat="1" spans="1:7">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="2">
+        <v>1002</v>
+      </c>
+      <c r="D16" s="2">
+        <v>3</v>
+      </c>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+    </row>
     <row r="17" customFormat="1" spans="1:7">
       <c r="A17" s="1"/>
       <c r="B17" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C17" s="2">
         <v>1003</v>
       </c>
       <c r="D17" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
@@ -1326,28 +1452,43 @@
     <row r="18" customFormat="1" spans="1:7">
       <c r="A18" s="1"/>
       <c r="B18" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C18" s="2">
         <v>1004</v>
       </c>
       <c r="D18" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
     </row>
+    <row r="19" customFormat="1" spans="1:7">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C19" s="2">
+        <v>1005</v>
+      </c>
+      <c r="D19" s="2">
+        <v>3</v>
+      </c>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+    </row>
     <row r="20" customFormat="1" spans="1:7">
       <c r="A20" s="1"/>
       <c r="B20" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C20" s="2">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="D20" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
@@ -1356,13 +1497,13 @@
     <row r="21" customFormat="1" spans="1:7">
       <c r="A21" s="1"/>
       <c r="B21" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C21" s="2">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="D21" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
@@ -1371,28 +1512,43 @@
     <row r="22" customFormat="1" spans="1:7">
       <c r="A22" s="1"/>
       <c r="B22" s="1" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C22" s="2">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="D22" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
     </row>
+    <row r="23" customFormat="1" spans="1:7">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C23" s="2">
+        <v>1004</v>
+      </c>
+      <c r="D23" s="2">
+        <v>4</v>
+      </c>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+    </row>
     <row r="24" customFormat="1" spans="1:7">
       <c r="A24" s="1"/>
       <c r="B24" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C24" s="2">
-        <v>1003</v>
+        <v>2001</v>
       </c>
       <c r="D24" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
@@ -1401,44 +1557,38 @@
     <row r="25" customFormat="1" spans="1:7">
       <c r="A25" s="1"/>
       <c r="B25" s="1" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="C25" s="2">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="D25" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
     </row>
-    <row r="26" customFormat="1" spans="1:7">
-      <c r="A26" s="1"/>
-      <c r="B26" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C26" s="2">
-        <v>1005</v>
-      </c>
-      <c r="D26" s="2">
-        <v>3</v>
-      </c>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
+    <row r="27" customFormat="1" spans="1:7">
+      <c r="A27" s="1"/>
+      <c r="B27" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C27" s="2">
+        <v>1001</v>
+      </c>
+      <c r="D27" s="2">
+        <v>5</v>
+      </c>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
     </row>
     <row r="28" customFormat="1" spans="1:7">
       <c r="A28" s="1"/>
-      <c r="B28" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C28" s="2">
-        <v>1001</v>
-      </c>
-      <c r="D28" s="2">
-        <v>4</v>
-      </c>
+      <c r="B28" s="1"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
@@ -1446,13 +1596,13 @@
     <row r="29" customFormat="1" spans="1:7">
       <c r="A29" s="1"/>
       <c r="B29" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C29" s="2">
         <v>1002</v>
       </c>
       <c r="D29" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
@@ -1460,30 +1610,33 @@
     </row>
     <row r="30" customFormat="1" spans="1:7">
       <c r="A30" s="1"/>
-      <c r="B30" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C30" s="2">
-        <v>1003</v>
-      </c>
-      <c r="D30" s="2">
-        <v>4</v>
-      </c>
+      <c r="B30" s="1"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
     </row>
+    <row r="31" customFormat="1" spans="1:7">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C31" s="2">
+        <v>1003</v>
+      </c>
+      <c r="D31" s="2">
+        <v>5</v>
+      </c>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+    </row>
     <row r="32" customFormat="1" spans="1:7">
       <c r="A32" s="1"/>
-      <c r="B32" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C32" s="3">
-        <v>1004</v>
-      </c>
-      <c r="D32" s="3">
-        <v>4</v>
-      </c>
+      <c r="B32" s="1"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
@@ -1491,13 +1644,13 @@
     <row r="33" customFormat="1" spans="1:7">
       <c r="A33" s="1"/>
       <c r="B33" s="1" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C33" s="2">
-        <v>2001</v>
+        <v>1004</v>
       </c>
       <c r="D33" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
@@ -1506,17 +1659,311 @@
     <row r="34" customFormat="1" spans="1:7">
       <c r="A34" s="1"/>
       <c r="B34" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C34" s="3">
+        <v>33</v>
+      </c>
+      <c r="C34" s="2">
         <v>1005</v>
       </c>
       <c r="D34" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
+    </row>
+    <row r="35" customFormat="1" spans="1:7">
+      <c r="A35" s="1"/>
+      <c r="B35" s="1"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+    </row>
+    <row r="36" customFormat="1" spans="1:7">
+      <c r="A36" s="1"/>
+      <c r="B36" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C36" s="2">
+        <v>1001</v>
+      </c>
+      <c r="D36" s="2">
+        <v>6</v>
+      </c>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+    </row>
+    <row r="37" customFormat="1" spans="1:7">
+      <c r="A37" s="1"/>
+      <c r="B37" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C37" s="2">
+        <v>1002</v>
+      </c>
+      <c r="D37" s="2">
+        <v>6</v>
+      </c>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+    </row>
+    <row r="38" customFormat="1" spans="1:7">
+      <c r="A38" s="1"/>
+      <c r="B38" s="1"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+    </row>
+    <row r="39" customFormat="1" spans="1:7">
+      <c r="A39" s="1"/>
+      <c r="B39" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C39" s="2">
+        <v>1003</v>
+      </c>
+      <c r="D39" s="2">
+        <v>6</v>
+      </c>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+    </row>
+    <row r="40" customFormat="1" spans="1:7">
+      <c r="A40" s="1"/>
+      <c r="B40" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C40" s="2">
+        <v>1004</v>
+      </c>
+      <c r="D40" s="2">
+        <v>6</v>
+      </c>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+    </row>
+    <row r="41" customFormat="1" spans="1:7">
+      <c r="A41" s="1"/>
+      <c r="B41" s="1"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
+    </row>
+    <row r="42" customFormat="1" spans="1:7">
+      <c r="A42" s="1"/>
+      <c r="B42" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C42" s="2">
+        <v>1005</v>
+      </c>
+      <c r="D42" s="2">
+        <v>6</v>
+      </c>
+      <c r="E42" s="2"/>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
+    </row>
+    <row r="43" customFormat="1" spans="1:7">
+      <c r="A43" s="1"/>
+      <c r="B43" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C43" s="2">
+        <v>1001</v>
+      </c>
+      <c r="D43" s="2">
+        <v>7</v>
+      </c>
+      <c r="E43" s="2"/>
+      <c r="F43" s="2"/>
+      <c r="G43" s="2"/>
+    </row>
+    <row r="44" customFormat="1" spans="1:7">
+      <c r="A44" s="1"/>
+      <c r="B44" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C44" s="2">
+        <v>1002</v>
+      </c>
+      <c r="D44" s="2">
+        <v>7</v>
+      </c>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
+      <c r="G44" s="2"/>
+    </row>
+    <row r="45" customFormat="1" spans="1:7">
+      <c r="A45" s="1"/>
+      <c r="B45" s="1"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2"/>
+      <c r="F45" s="2"/>
+      <c r="G45" s="2"/>
+    </row>
+    <row r="46" customFormat="1" spans="1:7">
+      <c r="A46" s="1"/>
+      <c r="B46" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C46" s="2">
+        <v>1003</v>
+      </c>
+      <c r="D46" s="2">
+        <v>7</v>
+      </c>
+      <c r="E46" s="2"/>
+      <c r="F46" s="2"/>
+      <c r="G46" s="2"/>
+    </row>
+    <row r="47" customFormat="1" spans="1:7">
+      <c r="A47" s="1"/>
+      <c r="B47" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C47" s="2">
+        <v>1004</v>
+      </c>
+      <c r="D47" s="2">
+        <v>7</v>
+      </c>
+      <c r="E47" s="2"/>
+      <c r="F47" s="2"/>
+      <c r="G47" s="2"/>
+    </row>
+    <row r="48" customFormat="1" spans="1:7">
+      <c r="A48" s="1"/>
+      <c r="B48" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C48" s="2">
+        <v>1005</v>
+      </c>
+      <c r="D48" s="2">
+        <v>7</v>
+      </c>
+      <c r="E48" s="2"/>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2"/>
+    </row>
+    <row r="49" customFormat="1" spans="1:7">
+      <c r="A49" s="1"/>
+      <c r="B49" s="1"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="2"/>
+      <c r="G49" s="2"/>
+    </row>
+    <row r="50" customFormat="1" spans="1:7">
+      <c r="A50" s="1"/>
+      <c r="B50" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C50" s="2">
+        <v>1001</v>
+      </c>
+      <c r="D50" s="2">
+        <v>8</v>
+      </c>
+      <c r="E50" s="2"/>
+      <c r="F50" s="2"/>
+      <c r="G50" s="2"/>
+    </row>
+    <row r="51" customFormat="1" spans="1:7">
+      <c r="A51" s="1"/>
+      <c r="B51" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C51" s="2">
+        <v>1002</v>
+      </c>
+      <c r="D51" s="2">
+        <v>8</v>
+      </c>
+      <c r="E51" s="2"/>
+      <c r="F51" s="2"/>
+      <c r="G51" s="2"/>
+    </row>
+    <row r="52" customFormat="1" spans="1:7">
+      <c r="A52" s="1"/>
+      <c r="B52" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C52" s="2">
+        <v>1003</v>
+      </c>
+      <c r="D52" s="2">
+        <v>8</v>
+      </c>
+      <c r="E52" s="2"/>
+      <c r="F52" s="2"/>
+      <c r="G52" s="2"/>
+    </row>
+    <row r="53" customFormat="1" spans="1:7">
+      <c r="A53" s="1"/>
+      <c r="B53" s="1"/>
+      <c r="C53" s="2"/>
+      <c r="D53" s="2"/>
+      <c r="E53" s="2"/>
+      <c r="F53" s="2"/>
+      <c r="G53" s="2"/>
+    </row>
+    <row r="54" customFormat="1" spans="1:7">
+      <c r="A54" s="1"/>
+      <c r="B54" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C54" s="2">
+        <v>1004</v>
+      </c>
+      <c r="D54" s="2">
+        <v>8</v>
+      </c>
+      <c r="E54" s="2"/>
+      <c r="F54" s="2"/>
+      <c r="G54" s="2"/>
+    </row>
+    <row r="55" customFormat="1" spans="1:7">
+      <c r="A55" s="1"/>
+      <c r="B55" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C55" s="2">
+        <v>2002</v>
+      </c>
+      <c r="D55" s="2">
+        <v>1</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" s="2"/>
+      <c r="G55" s="2"/>
+    </row>
+    <row r="56" customFormat="1" spans="1:7">
+      <c r="A56" s="1"/>
+      <c r="B56" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C56" s="2">
+        <v>1005</v>
+      </c>
+      <c r="D56" s="2">
+        <v>8</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" s="2"/>
+      <c r="G56" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/MonsterGroupConfig.xlsx
+++ b/Config/MonsterGroupConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="6855" windowHeight="14775"/>
+    <workbookView windowWidth="8940" windowHeight="11805"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -381,12 +381,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1200,12 +1200,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="9.775" style="1" customWidth="1"/>
-    <col min="3" max="7" width="9.88333333333333" style="2" customWidth="1"/>
+    <col min="1" max="1" width="5.75" style="1" customWidth="1"/>
+    <col min="2" max="2" width="6.3" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.45" style="2" customWidth="1"/>
+    <col min="4" max="4" width="8.03333333333333" style="2" customWidth="1"/>
+    <col min="5" max="7" width="9.88333333333333" style="2" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1586,9 +1588,15 @@
     </row>
     <row r="28" customFormat="1" spans="1:7">
       <c r="A28" s="1"/>
-      <c r="B28" s="1"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
+      <c r="B28" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C28" s="2">
+        <v>1002</v>
+      </c>
+      <c r="D28" s="2">
+        <v>5</v>
+      </c>
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
@@ -1596,10 +1604,10 @@
     <row r="29" customFormat="1" spans="1:7">
       <c r="A29" s="1"/>
       <c r="B29" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C29" s="2">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="D29" s="2">
         <v>5</v>
@@ -1610,9 +1618,15 @@
     </row>
     <row r="30" customFormat="1" spans="1:7">
       <c r="A30" s="1"/>
-      <c r="B30" s="1"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
+      <c r="B30" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C30" s="2">
+        <v>1004</v>
+      </c>
+      <c r="D30" s="2">
+        <v>5</v>
+      </c>
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
@@ -1620,10 +1634,10 @@
     <row r="31" customFormat="1" spans="1:7">
       <c r="A31" s="1"/>
       <c r="B31" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C31" s="2">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="D31" s="2">
         <v>5</v>
@@ -1634,9 +1648,15 @@
     </row>
     <row r="32" customFormat="1" spans="1:7">
       <c r="A32" s="1"/>
-      <c r="B32" s="1"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
+      <c r="B32" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C32" s="2">
+        <v>1001</v>
+      </c>
+      <c r="D32" s="2">
+        <v>6</v>
+      </c>
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
@@ -1644,13 +1664,13 @@
     <row r="33" customFormat="1" spans="1:7">
       <c r="A33" s="1"/>
       <c r="B33" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C33" s="2">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="D33" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
@@ -1659,13 +1679,13 @@
     <row r="34" customFormat="1" spans="1:7">
       <c r="A34" s="1"/>
       <c r="B34" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C34" s="2">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="D34" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" s="2"/>
@@ -1673,9 +1693,15 @@
     </row>
     <row r="35" customFormat="1" spans="1:7">
       <c r="A35" s="1"/>
-      <c r="B35" s="1"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
+      <c r="B35" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C35" s="2">
+        <v>1004</v>
+      </c>
+      <c r="D35" s="2">
+        <v>6</v>
+      </c>
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
@@ -1683,10 +1709,10 @@
     <row r="36" customFormat="1" spans="1:7">
       <c r="A36" s="1"/>
       <c r="B36" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C36" s="2">
-        <v>1001</v>
+        <v>1005</v>
       </c>
       <c r="D36" s="2">
         <v>6</v>
@@ -1698,13 +1724,13 @@
     <row r="37" customFormat="1" spans="1:7">
       <c r="A37" s="1"/>
       <c r="B37" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C37" s="2">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="D37" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
@@ -1712,9 +1738,15 @@
     </row>
     <row r="38" customFormat="1" spans="1:7">
       <c r="A38" s="1"/>
-      <c r="B38" s="1"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
+      <c r="B38" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C38" s="2">
+        <v>1002</v>
+      </c>
+      <c r="D38" s="2">
+        <v>7</v>
+      </c>
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
@@ -1722,13 +1754,13 @@
     <row r="39" customFormat="1" spans="1:7">
       <c r="A39" s="1"/>
       <c r="B39" s="1" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C39" s="2">
         <v>1003</v>
       </c>
       <c r="D39" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
@@ -1737,13 +1769,13 @@
     <row r="40" customFormat="1" spans="1:7">
       <c r="A40" s="1"/>
       <c r="B40" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C40" s="2">
         <v>1004</v>
       </c>
       <c r="D40" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
@@ -1751,9 +1783,15 @@
     </row>
     <row r="41" customFormat="1" spans="1:7">
       <c r="A41" s="1"/>
-      <c r="B41" s="1"/>
-      <c r="C41" s="2"/>
-      <c r="D41" s="2"/>
+      <c r="B41" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C41" s="2">
+        <v>1005</v>
+      </c>
+      <c r="D41" s="2">
+        <v>7</v>
+      </c>
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
@@ -1761,13 +1799,13 @@
     <row r="42" customFormat="1" spans="1:7">
       <c r="A42" s="1"/>
       <c r="B42" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C42" s="2">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="D42" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
@@ -1776,13 +1814,13 @@
     <row r="43" customFormat="1" spans="1:7">
       <c r="A43" s="1"/>
       <c r="B43" s="1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C43" s="2">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="D43" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
@@ -1791,13 +1829,13 @@
     <row r="44" customFormat="1" spans="1:7">
       <c r="A44" s="1"/>
       <c r="B44" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C44" s="2">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="D44" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
@@ -1805,9 +1843,15 @@
     </row>
     <row r="45" customFormat="1" spans="1:7">
       <c r="A45" s="1"/>
-      <c r="B45" s="1"/>
-      <c r="C45" s="2"/>
-      <c r="D45" s="2"/>
+      <c r="B45" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C45" s="2">
+        <v>1004</v>
+      </c>
+      <c r="D45" s="2">
+        <v>8</v>
+      </c>
       <c r="E45" s="2"/>
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
@@ -1815,13 +1859,13 @@
     <row r="46" customFormat="1" spans="1:7">
       <c r="A46" s="1"/>
       <c r="B46" s="1" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C46" s="2">
-        <v>1003</v>
+        <v>2001</v>
       </c>
       <c r="D46" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
@@ -1830,140 +1874,17 @@
     <row r="47" customFormat="1" spans="1:7">
       <c r="A47" s="1"/>
       <c r="B47" s="1" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C47" s="2">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="D47" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
-    </row>
-    <row r="48" customFormat="1" spans="1:7">
-      <c r="A48" s="1"/>
-      <c r="B48" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C48" s="2">
-        <v>1005</v>
-      </c>
-      <c r="D48" s="2">
-        <v>7</v>
-      </c>
-      <c r="E48" s="2"/>
-      <c r="F48" s="2"/>
-      <c r="G48" s="2"/>
-    </row>
-    <row r="49" customFormat="1" spans="1:7">
-      <c r="A49" s="1"/>
-      <c r="B49" s="1"/>
-      <c r="C49" s="2"/>
-      <c r="D49" s="2"/>
-      <c r="E49" s="2"/>
-      <c r="F49" s="2"/>
-      <c r="G49" s="2"/>
-    </row>
-    <row r="50" customFormat="1" spans="1:7">
-      <c r="A50" s="1"/>
-      <c r="B50" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C50" s="2">
-        <v>1001</v>
-      </c>
-      <c r="D50" s="2">
-        <v>8</v>
-      </c>
-      <c r="E50" s="2"/>
-      <c r="F50" s="2"/>
-      <c r="G50" s="2"/>
-    </row>
-    <row r="51" customFormat="1" spans="1:7">
-      <c r="A51" s="1"/>
-      <c r="B51" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C51" s="2">
-        <v>1002</v>
-      </c>
-      <c r="D51" s="2">
-        <v>8</v>
-      </c>
-      <c r="E51" s="2"/>
-      <c r="F51" s="2"/>
-      <c r="G51" s="2"/>
-    </row>
-    <row r="52" customFormat="1" spans="1:7">
-      <c r="A52" s="1"/>
-      <c r="B52" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C52" s="2">
-        <v>1003</v>
-      </c>
-      <c r="D52" s="2">
-        <v>8</v>
-      </c>
-      <c r="E52" s="2"/>
-      <c r="F52" s="2"/>
-      <c r="G52" s="2"/>
-    </row>
-    <row r="53" customFormat="1" spans="1:7">
-      <c r="A53" s="1"/>
-      <c r="B53" s="1"/>
-      <c r="C53" s="2"/>
-      <c r="D53" s="2"/>
-      <c r="E53" s="2"/>
-      <c r="F53" s="2"/>
-      <c r="G53" s="2"/>
-    </row>
-    <row r="54" customFormat="1" spans="1:7">
-      <c r="A54" s="1"/>
-      <c r="B54" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C54" s="2">
-        <v>1004</v>
-      </c>
-      <c r="D54" s="2">
-        <v>8</v>
-      </c>
-      <c r="E54" s="2"/>
-      <c r="F54" s="2"/>
-      <c r="G54" s="2"/>
-    </row>
-    <row r="55" customFormat="1" spans="1:7">
-      <c r="A55" s="1"/>
-      <c r="B55" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C55" s="2">
-        <v>2002</v>
-      </c>
-      <c r="D55" s="2">
-        <v>1</v>
-      </c>
-      <c r="E55" s="2"/>
-      <c r="F55" s="2"/>
-      <c r="G55" s="2"/>
-    </row>
-    <row r="56" customFormat="1" spans="1:7">
-      <c r="A56" s="1"/>
-      <c r="B56" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C56" s="2">
-        <v>1005</v>
-      </c>
-      <c r="D56" s="2">
-        <v>8</v>
-      </c>
-      <c r="E56" s="2"/>
-      <c r="F56" s="2"/>
-      <c r="G56" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/MonsterGroupConfig.xlsx
+++ b/Config/MonsterGroupConfig.xlsx
@@ -1066,7 +1066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G245"/>
+  <dimension ref="A1:G644"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="5.75" customWidth="1" style="1" min="1" max="1"/>
@@ -3782,6 +3782,4395 @@
         <v>44</v>
       </c>
     </row>
+    <row r="246">
+      <c r="B246" s="0" t="n">
+        <v>120011</v>
+      </c>
+      <c r="C246" s="0" t="n">
+        <v>1006</v>
+      </c>
+      <c r="D246" s="0" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="B247" s="0" t="n">
+        <v>120021</v>
+      </c>
+      <c r="C247" s="0" t="n">
+        <v>1007</v>
+      </c>
+      <c r="D247" s="0" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="B248" s="0" t="n">
+        <v>120031</v>
+      </c>
+      <c r="C248" s="0" t="n">
+        <v>1008</v>
+      </c>
+      <c r="D248" s="0" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="B249" s="0" t="n">
+        <v>120041</v>
+      </c>
+      <c r="C249" s="0" t="n">
+        <v>1009</v>
+      </c>
+      <c r="D249" s="0" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="B250" s="0" t="n">
+        <v>120042</v>
+      </c>
+      <c r="C250" s="0" t="n">
+        <v>3005</v>
+      </c>
+      <c r="D250" s="0" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="B251" s="0" t="n">
+        <v>120051</v>
+      </c>
+      <c r="C251" s="0" t="n">
+        <v>1010</v>
+      </c>
+      <c r="D251" s="0" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="B252" s="0" t="n">
+        <v>120052</v>
+      </c>
+      <c r="C252" s="0" t="n">
+        <v>3005</v>
+      </c>
+      <c r="D252" s="0" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="B253" s="0" t="n">
+        <v>120061</v>
+      </c>
+      <c r="C253" s="0" t="n">
+        <v>1011</v>
+      </c>
+      <c r="D253" s="0" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="B254" s="0" t="n">
+        <v>120062</v>
+      </c>
+      <c r="C254" s="0" t="n">
+        <v>3005</v>
+      </c>
+      <c r="D254" s="0" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="B255" s="0" t="n">
+        <v>120071</v>
+      </c>
+      <c r="C255" s="0" t="n">
+        <v>3005</v>
+      </c>
+      <c r="D255" s="0" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="B256" s="0" t="n">
+        <v>120072</v>
+      </c>
+      <c r="C256" s="0" t="n">
+        <v>1002</v>
+      </c>
+      <c r="D256" s="0" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="B257" s="0" t="n">
+        <v>120073</v>
+      </c>
+      <c r="C257" s="0" t="n">
+        <v>1003</v>
+      </c>
+      <c r="D257" s="0" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="B258" s="0" t="n">
+        <v>120081</v>
+      </c>
+      <c r="C258" s="0" t="n">
+        <v>3005</v>
+      </c>
+      <c r="D258" s="0" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="B259" s="0" t="n">
+        <v>120082</v>
+      </c>
+      <c r="C259" s="0" t="n">
+        <v>1003</v>
+      </c>
+      <c r="D259" s="0" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="B260" s="0" t="n">
+        <v>120083</v>
+      </c>
+      <c r="C260" s="0" t="n">
+        <v>1004</v>
+      </c>
+      <c r="D260" s="0" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="B261" s="0" t="n">
+        <v>120091</v>
+      </c>
+      <c r="C261" s="0" t="n">
+        <v>3005</v>
+      </c>
+      <c r="D261" s="0" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="B262" s="0" t="n">
+        <v>120092</v>
+      </c>
+      <c r="C262" s="0" t="n">
+        <v>1004</v>
+      </c>
+      <c r="D262" s="0" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="B263" s="0" t="n">
+        <v>120093</v>
+      </c>
+      <c r="C263" s="0" t="n">
+        <v>1005</v>
+      </c>
+      <c r="D263" s="0" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="B264" s="0" t="n">
+        <v>120101</v>
+      </c>
+      <c r="C264" s="0" t="n">
+        <v>2004</v>
+      </c>
+      <c r="D264" s="0" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="B265" s="0" t="n">
+        <v>120102</v>
+      </c>
+      <c r="C265" s="0" t="n">
+        <v>3005</v>
+      </c>
+      <c r="D265" s="0" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="B266" s="0" t="n">
+        <v>120103</v>
+      </c>
+      <c r="C266" s="0" t="n">
+        <v>1006</v>
+      </c>
+      <c r="D266" s="0" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="B267" s="0" t="n">
+        <v>130011</v>
+      </c>
+      <c r="C267" s="0" t="n">
+        <v>1009</v>
+      </c>
+      <c r="D267" s="0" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="B268" s="0" t="n">
+        <v>130021</v>
+      </c>
+      <c r="C268" s="0" t="n">
+        <v>1010</v>
+      </c>
+      <c r="D268" s="0" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="B269" s="0" t="n">
+        <v>130031</v>
+      </c>
+      <c r="C269" s="0" t="n">
+        <v>1011</v>
+      </c>
+      <c r="D269" s="0" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="B270" s="0" t="n">
+        <v>130041</v>
+      </c>
+      <c r="C270" s="0" t="n">
+        <v>1001</v>
+      </c>
+      <c r="D270" s="0" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="B271" s="0" t="n">
+        <v>130042</v>
+      </c>
+      <c r="C271" s="0" t="n">
+        <v>3006</v>
+      </c>
+      <c r="D271" s="0" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="B272" s="0" t="n">
+        <v>130051</v>
+      </c>
+      <c r="C272" s="0" t="n">
+        <v>1002</v>
+      </c>
+      <c r="D272" s="0" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="B273" s="0" t="n">
+        <v>130052</v>
+      </c>
+      <c r="C273" s="0" t="n">
+        <v>3006</v>
+      </c>
+      <c r="D273" s="0" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="B274" s="0" t="n">
+        <v>130061</v>
+      </c>
+      <c r="C274" s="0" t="n">
+        <v>1003</v>
+      </c>
+      <c r="D274" s="0" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="B275" s="0" t="n">
+        <v>130062</v>
+      </c>
+      <c r="C275" s="0" t="n">
+        <v>3006</v>
+      </c>
+      <c r="D275" s="0" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="B276" s="0" t="n">
+        <v>130071</v>
+      </c>
+      <c r="C276" s="0" t="n">
+        <v>3006</v>
+      </c>
+      <c r="D276" s="0" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="B277" s="0" t="n">
+        <v>130072</v>
+      </c>
+      <c r="C277" s="0" t="n">
+        <v>1005</v>
+      </c>
+      <c r="D277" s="0" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="B278" s="0" t="n">
+        <v>130073</v>
+      </c>
+      <c r="C278" s="0" t="n">
+        <v>1006</v>
+      </c>
+      <c r="D278" s="0" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="B279" s="0" t="n">
+        <v>130081</v>
+      </c>
+      <c r="C279" s="0" t="n">
+        <v>3006</v>
+      </c>
+      <c r="D279" s="0" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="B280" s="0" t="n">
+        <v>130082</v>
+      </c>
+      <c r="C280" s="0" t="n">
+        <v>1006</v>
+      </c>
+      <c r="D280" s="0" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="B281" s="0" t="n">
+        <v>130083</v>
+      </c>
+      <c r="C281" s="0" t="n">
+        <v>1007</v>
+      </c>
+      <c r="D281" s="0" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="B282" s="0" t="n">
+        <v>130091</v>
+      </c>
+      <c r="C282" s="0" t="n">
+        <v>3006</v>
+      </c>
+      <c r="D282" s="0" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="B283" s="0" t="n">
+        <v>130092</v>
+      </c>
+      <c r="C283" s="0" t="n">
+        <v>1007</v>
+      </c>
+      <c r="D283" s="0" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="B284" s="0" t="n">
+        <v>130093</v>
+      </c>
+      <c r="C284" s="0" t="n">
+        <v>1008</v>
+      </c>
+      <c r="D284" s="0" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="B285" s="0" t="n">
+        <v>130101</v>
+      </c>
+      <c r="C285" s="0" t="n">
+        <v>2005</v>
+      </c>
+      <c r="D285" s="0" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="B286" s="0" t="n">
+        <v>130102</v>
+      </c>
+      <c r="C286" s="0" t="n">
+        <v>3006</v>
+      </c>
+      <c r="D286" s="0" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="B287" s="0" t="n">
+        <v>130103</v>
+      </c>
+      <c r="C287" s="0" t="n">
+        <v>1009</v>
+      </c>
+      <c r="D287" s="0" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="B288" s="0" t="n">
+        <v>140011</v>
+      </c>
+      <c r="C288" s="0" t="n">
+        <v>1001</v>
+      </c>
+      <c r="D288" s="0" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="B289" s="0" t="n">
+        <v>140021</v>
+      </c>
+      <c r="C289" s="0" t="n">
+        <v>1002</v>
+      </c>
+      <c r="D289" s="0" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="B290" s="0" t="n">
+        <v>140031</v>
+      </c>
+      <c r="C290" s="0" t="n">
+        <v>1003</v>
+      </c>
+      <c r="D290" s="0" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="B291" s="0" t="n">
+        <v>140041</v>
+      </c>
+      <c r="C291" s="0" t="n">
+        <v>1004</v>
+      </c>
+      <c r="D291" s="0" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="B292" s="0" t="n">
+        <v>140042</v>
+      </c>
+      <c r="C292" s="0" t="n">
+        <v>3007</v>
+      </c>
+      <c r="D292" s="0" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="B293" s="0" t="n">
+        <v>140051</v>
+      </c>
+      <c r="C293" s="0" t="n">
+        <v>1005</v>
+      </c>
+      <c r="D293" s="0" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="B294" s="0" t="n">
+        <v>140052</v>
+      </c>
+      <c r="C294" s="0" t="n">
+        <v>3007</v>
+      </c>
+      <c r="D294" s="0" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="B295" s="0" t="n">
+        <v>140061</v>
+      </c>
+      <c r="C295" s="0" t="n">
+        <v>1006</v>
+      </c>
+      <c r="D295" s="0" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="B296" s="0" t="n">
+        <v>140062</v>
+      </c>
+      <c r="C296" s="0" t="n">
+        <v>3007</v>
+      </c>
+      <c r="D296" s="0" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="B297" s="0" t="n">
+        <v>140071</v>
+      </c>
+      <c r="C297" s="0" t="n">
+        <v>3007</v>
+      </c>
+      <c r="D297" s="0" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="B298" s="0" t="n">
+        <v>140072</v>
+      </c>
+      <c r="C298" s="0" t="n">
+        <v>1008</v>
+      </c>
+      <c r="D298" s="0" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="B299" s="0" t="n">
+        <v>140073</v>
+      </c>
+      <c r="C299" s="0" t="n">
+        <v>1009</v>
+      </c>
+      <c r="D299" s="0" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="B300" s="0" t="n">
+        <v>140081</v>
+      </c>
+      <c r="C300" s="0" t="n">
+        <v>3007</v>
+      </c>
+      <c r="D300" s="0" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="B301" s="0" t="n">
+        <v>140082</v>
+      </c>
+      <c r="C301" s="0" t="n">
+        <v>1009</v>
+      </c>
+      <c r="D301" s="0" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="B302" s="0" t="n">
+        <v>140083</v>
+      </c>
+      <c r="C302" s="0" t="n">
+        <v>1010</v>
+      </c>
+      <c r="D302" s="0" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="B303" s="0" t="n">
+        <v>140091</v>
+      </c>
+      <c r="C303" s="0" t="n">
+        <v>3007</v>
+      </c>
+      <c r="D303" s="0" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="B304" s="0" t="n">
+        <v>140092</v>
+      </c>
+      <c r="C304" s="0" t="n">
+        <v>1010</v>
+      </c>
+      <c r="D304" s="0" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="B305" s="0" t="n">
+        <v>140093</v>
+      </c>
+      <c r="C305" s="0" t="n">
+        <v>1011</v>
+      </c>
+      <c r="D305" s="0" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="B306" s="0" t="n">
+        <v>140101</v>
+      </c>
+      <c r="C306" s="0" t="n">
+        <v>2006</v>
+      </c>
+      <c r="D306" s="0" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="B307" s="0" t="n">
+        <v>140102</v>
+      </c>
+      <c r="C307" s="0" t="n">
+        <v>3007</v>
+      </c>
+      <c r="D307" s="0" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="B308" s="0" t="n">
+        <v>140103</v>
+      </c>
+      <c r="C308" s="0" t="n">
+        <v>1001</v>
+      </c>
+      <c r="D308" s="0" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="B309" s="0" t="n">
+        <v>150011</v>
+      </c>
+      <c r="C309" s="0" t="n">
+        <v>1004</v>
+      </c>
+      <c r="D309" s="0" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="B310" s="0" t="n">
+        <v>150021</v>
+      </c>
+      <c r="C310" s="0" t="n">
+        <v>1005</v>
+      </c>
+      <c r="D310" s="0" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="B311" s="0" t="n">
+        <v>150031</v>
+      </c>
+      <c r="C311" s="0" t="n">
+        <v>1006</v>
+      </c>
+      <c r="D311" s="0" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="B312" s="0" t="n">
+        <v>150041</v>
+      </c>
+      <c r="C312" s="0" t="n">
+        <v>1007</v>
+      </c>
+      <c r="D312" s="0" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="B313" s="0" t="n">
+        <v>150042</v>
+      </c>
+      <c r="C313" s="0" t="n">
+        <v>3008</v>
+      </c>
+      <c r="D313" s="0" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="B314" s="0" t="n">
+        <v>150051</v>
+      </c>
+      <c r="C314" s="0" t="n">
+        <v>1008</v>
+      </c>
+      <c r="D314" s="0" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="B315" s="0" t="n">
+        <v>150052</v>
+      </c>
+      <c r="C315" s="0" t="n">
+        <v>3008</v>
+      </c>
+      <c r="D315" s="0" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="B316" s="0" t="n">
+        <v>150061</v>
+      </c>
+      <c r="C316" s="0" t="n">
+        <v>1009</v>
+      </c>
+      <c r="D316" s="0" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="B317" s="0" t="n">
+        <v>150062</v>
+      </c>
+      <c r="C317" s="0" t="n">
+        <v>3008</v>
+      </c>
+      <c r="D317" s="0" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="B318" s="0" t="n">
+        <v>150071</v>
+      </c>
+      <c r="C318" s="0" t="n">
+        <v>3008</v>
+      </c>
+      <c r="D318" s="0" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="B319" s="0" t="n">
+        <v>150072</v>
+      </c>
+      <c r="C319" s="0" t="n">
+        <v>1011</v>
+      </c>
+      <c r="D319" s="0" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="B320" s="0" t="n">
+        <v>150073</v>
+      </c>
+      <c r="C320" s="0" t="n">
+        <v>1001</v>
+      </c>
+      <c r="D320" s="0" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="B321" s="0" t="n">
+        <v>150081</v>
+      </c>
+      <c r="C321" s="0" t="n">
+        <v>3008</v>
+      </c>
+      <c r="D321" s="0" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="B322" s="0" t="n">
+        <v>150082</v>
+      </c>
+      <c r="C322" s="0" t="n">
+        <v>1001</v>
+      </c>
+      <c r="D322" s="0" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="B323" s="0" t="n">
+        <v>150083</v>
+      </c>
+      <c r="C323" s="0" t="n">
+        <v>1002</v>
+      </c>
+      <c r="D323" s="0" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="B324" s="0" t="n">
+        <v>150091</v>
+      </c>
+      <c r="C324" s="0" t="n">
+        <v>3008</v>
+      </c>
+      <c r="D324" s="0" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="B325" s="0" t="n">
+        <v>150092</v>
+      </c>
+      <c r="C325" s="0" t="n">
+        <v>1002</v>
+      </c>
+      <c r="D325" s="0" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="B326" s="0" t="n">
+        <v>150093</v>
+      </c>
+      <c r="C326" s="0" t="n">
+        <v>1003</v>
+      </c>
+      <c r="D326" s="0" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="B327" s="0" t="n">
+        <v>150101</v>
+      </c>
+      <c r="C327" s="0" t="n">
+        <v>2007</v>
+      </c>
+      <c r="D327" s="0" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="B328" s="0" t="n">
+        <v>150102</v>
+      </c>
+      <c r="C328" s="0" t="n">
+        <v>3008</v>
+      </c>
+      <c r="D328" s="0" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="B329" s="0" t="n">
+        <v>150103</v>
+      </c>
+      <c r="C329" s="0" t="n">
+        <v>1004</v>
+      </c>
+      <c r="D329" s="0" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="B330" s="0" t="n">
+        <v>160011</v>
+      </c>
+      <c r="C330" s="0" t="n">
+        <v>1007</v>
+      </c>
+      <c r="D330" s="0" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="B331" s="0" t="n">
+        <v>160021</v>
+      </c>
+      <c r="C331" s="0" t="n">
+        <v>1008</v>
+      </c>
+      <c r="D331" s="0" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="B332" s="0" t="n">
+        <v>160031</v>
+      </c>
+      <c r="C332" s="0" t="n">
+        <v>1009</v>
+      </c>
+      <c r="D332" s="0" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="B333" s="0" t="n">
+        <v>160041</v>
+      </c>
+      <c r="C333" s="0" t="n">
+        <v>1010</v>
+      </c>
+      <c r="D333" s="0" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="B334" s="0" t="n">
+        <v>160042</v>
+      </c>
+      <c r="C334" s="0" t="n">
+        <v>3001</v>
+      </c>
+      <c r="D334" s="0" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="B335" s="0" t="n">
+        <v>160051</v>
+      </c>
+      <c r="C335" s="0" t="n">
+        <v>1011</v>
+      </c>
+      <c r="D335" s="0" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="B336" s="0" t="n">
+        <v>160052</v>
+      </c>
+      <c r="C336" s="0" t="n">
+        <v>3001</v>
+      </c>
+      <c r="D336" s="0" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="B337" s="0" t="n">
+        <v>160061</v>
+      </c>
+      <c r="C337" s="0" t="n">
+        <v>1001</v>
+      </c>
+      <c r="D337" s="0" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="B338" s="0" t="n">
+        <v>160062</v>
+      </c>
+      <c r="C338" s="0" t="n">
+        <v>3001</v>
+      </c>
+      <c r="D338" s="0" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="B339" s="0" t="n">
+        <v>160071</v>
+      </c>
+      <c r="C339" s="0" t="n">
+        <v>3001</v>
+      </c>
+      <c r="D339" s="0" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="B340" s="0" t="n">
+        <v>160072</v>
+      </c>
+      <c r="C340" s="0" t="n">
+        <v>1003</v>
+      </c>
+      <c r="D340" s="0" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="B341" s="0" t="n">
+        <v>160073</v>
+      </c>
+      <c r="C341" s="0" t="n">
+        <v>1004</v>
+      </c>
+      <c r="D341" s="0" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="B342" s="0" t="n">
+        <v>160081</v>
+      </c>
+      <c r="C342" s="0" t="n">
+        <v>3001</v>
+      </c>
+      <c r="D342" s="0" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="B343" s="0" t="n">
+        <v>160082</v>
+      </c>
+      <c r="C343" s="0" t="n">
+        <v>1004</v>
+      </c>
+      <c r="D343" s="0" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="B344" s="0" t="n">
+        <v>160083</v>
+      </c>
+      <c r="C344" s="0" t="n">
+        <v>1005</v>
+      </c>
+      <c r="D344" s="0" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="B345" s="0" t="n">
+        <v>160091</v>
+      </c>
+      <c r="C345" s="0" t="n">
+        <v>3001</v>
+      </c>
+      <c r="D345" s="0" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="B346" s="0" t="n">
+        <v>160092</v>
+      </c>
+      <c r="C346" s="0" t="n">
+        <v>1005</v>
+      </c>
+      <c r="D346" s="0" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="B347" s="0" t="n">
+        <v>160093</v>
+      </c>
+      <c r="C347" s="0" t="n">
+        <v>1006</v>
+      </c>
+      <c r="D347" s="0" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="B348" s="0" t="n">
+        <v>160101</v>
+      </c>
+      <c r="C348" s="0" t="n">
+        <v>2008</v>
+      </c>
+      <c r="D348" s="0" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="B349" s="0" t="n">
+        <v>160102</v>
+      </c>
+      <c r="C349" s="0" t="n">
+        <v>3001</v>
+      </c>
+      <c r="D349" s="0" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="B350" s="0" t="n">
+        <v>160103</v>
+      </c>
+      <c r="C350" s="0" t="n">
+        <v>1007</v>
+      </c>
+      <c r="D350" s="0" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="B351" s="0" t="n">
+        <v>170011</v>
+      </c>
+      <c r="C351" s="0" t="n">
+        <v>1010</v>
+      </c>
+      <c r="D351" s="0" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="B352" s="0" t="n">
+        <v>170021</v>
+      </c>
+      <c r="C352" s="0" t="n">
+        <v>1011</v>
+      </c>
+      <c r="D352" s="0" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="B353" s="0" t="n">
+        <v>170031</v>
+      </c>
+      <c r="C353" s="0" t="n">
+        <v>1001</v>
+      </c>
+      <c r="D353" s="0" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="B354" s="0" t="n">
+        <v>170041</v>
+      </c>
+      <c r="C354" s="0" t="n">
+        <v>1002</v>
+      </c>
+      <c r="D354" s="0" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="B355" s="0" t="n">
+        <v>170042</v>
+      </c>
+      <c r="C355" s="0" t="n">
+        <v>3002</v>
+      </c>
+      <c r="D355" s="0" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="B356" s="0" t="n">
+        <v>170051</v>
+      </c>
+      <c r="C356" s="0" t="n">
+        <v>1003</v>
+      </c>
+      <c r="D356" s="0" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="B357" s="0" t="n">
+        <v>170052</v>
+      </c>
+      <c r="C357" s="0" t="n">
+        <v>3002</v>
+      </c>
+      <c r="D357" s="0" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="B358" s="0" t="n">
+        <v>170061</v>
+      </c>
+      <c r="C358" s="0" t="n">
+        <v>1004</v>
+      </c>
+      <c r="D358" s="0" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="B359" s="0" t="n">
+        <v>170062</v>
+      </c>
+      <c r="C359" s="0" t="n">
+        <v>3002</v>
+      </c>
+      <c r="D359" s="0" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="B360" s="0" t="n">
+        <v>170071</v>
+      </c>
+      <c r="C360" s="0" t="n">
+        <v>3002</v>
+      </c>
+      <c r="D360" s="0" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="B361" s="0" t="n">
+        <v>170072</v>
+      </c>
+      <c r="C361" s="0" t="n">
+        <v>1006</v>
+      </c>
+      <c r="D361" s="0" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="B362" s="0" t="n">
+        <v>170073</v>
+      </c>
+      <c r="C362" s="0" t="n">
+        <v>1007</v>
+      </c>
+      <c r="D362" s="0" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="B363" s="0" t="n">
+        <v>170081</v>
+      </c>
+      <c r="C363" s="0" t="n">
+        <v>3002</v>
+      </c>
+      <c r="D363" s="0" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="B364" s="0" t="n">
+        <v>170082</v>
+      </c>
+      <c r="C364" s="0" t="n">
+        <v>1007</v>
+      </c>
+      <c r="D364" s="0" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="B365" s="0" t="n">
+        <v>170083</v>
+      </c>
+      <c r="C365" s="0" t="n">
+        <v>1008</v>
+      </c>
+      <c r="D365" s="0" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="B366" s="0" t="n">
+        <v>170091</v>
+      </c>
+      <c r="C366" s="0" t="n">
+        <v>3002</v>
+      </c>
+      <c r="D366" s="0" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="B367" s="0" t="n">
+        <v>170092</v>
+      </c>
+      <c r="C367" s="0" t="n">
+        <v>1008</v>
+      </c>
+      <c r="D367" s="0" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="B368" s="0" t="n">
+        <v>170093</v>
+      </c>
+      <c r="C368" s="0" t="n">
+        <v>1009</v>
+      </c>
+      <c r="D368" s="0" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="B369" s="0" t="n">
+        <v>170101</v>
+      </c>
+      <c r="C369" s="0" t="n">
+        <v>2001</v>
+      </c>
+      <c r="D369" s="0" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="B370" s="0" t="n">
+        <v>170102</v>
+      </c>
+      <c r="C370" s="0" t="n">
+        <v>3002</v>
+      </c>
+      <c r="D370" s="0" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="B371" s="0" t="n">
+        <v>170103</v>
+      </c>
+      <c r="C371" s="0" t="n">
+        <v>1010</v>
+      </c>
+      <c r="D371" s="0" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="B372" s="0" t="n">
+        <v>180011</v>
+      </c>
+      <c r="C372" s="0" t="n">
+        <v>1002</v>
+      </c>
+      <c r="D372" s="0" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="B373" s="0" t="n">
+        <v>180021</v>
+      </c>
+      <c r="C373" s="0" t="n">
+        <v>1003</v>
+      </c>
+      <c r="D373" s="0" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="B374" s="0" t="n">
+        <v>180031</v>
+      </c>
+      <c r="C374" s="0" t="n">
+        <v>1004</v>
+      </c>
+      <c r="D374" s="0" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="B375" s="0" t="n">
+        <v>180041</v>
+      </c>
+      <c r="C375" s="0" t="n">
+        <v>1005</v>
+      </c>
+      <c r="D375" s="0" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="B376" s="0" t="n">
+        <v>180042</v>
+      </c>
+      <c r="C376" s="0" t="n">
+        <v>3003</v>
+      </c>
+      <c r="D376" s="0" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="B377" s="0" t="n">
+        <v>180051</v>
+      </c>
+      <c r="C377" s="0" t="n">
+        <v>1006</v>
+      </c>
+      <c r="D377" s="0" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="B378" s="0" t="n">
+        <v>180052</v>
+      </c>
+      <c r="C378" s="0" t="n">
+        <v>3003</v>
+      </c>
+      <c r="D378" s="0" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="B379" s="0" t="n">
+        <v>180061</v>
+      </c>
+      <c r="C379" s="0" t="n">
+        <v>1007</v>
+      </c>
+      <c r="D379" s="0" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="B380" s="0" t="n">
+        <v>180062</v>
+      </c>
+      <c r="C380" s="0" t="n">
+        <v>3003</v>
+      </c>
+      <c r="D380" s="0" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="B381" s="0" t="n">
+        <v>180071</v>
+      </c>
+      <c r="C381" s="0" t="n">
+        <v>3003</v>
+      </c>
+      <c r="D381" s="0" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="B382" s="0" t="n">
+        <v>180072</v>
+      </c>
+      <c r="C382" s="0" t="n">
+        <v>1009</v>
+      </c>
+      <c r="D382" s="0" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="B383" s="0" t="n">
+        <v>180073</v>
+      </c>
+      <c r="C383" s="0" t="n">
+        <v>1010</v>
+      </c>
+      <c r="D383" s="0" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="B384" s="0" t="n">
+        <v>180081</v>
+      </c>
+      <c r="C384" s="0" t="n">
+        <v>3003</v>
+      </c>
+      <c r="D384" s="0" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="B385" s="0" t="n">
+        <v>180082</v>
+      </c>
+      <c r="C385" s="0" t="n">
+        <v>1010</v>
+      </c>
+      <c r="D385" s="0" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="B386" s="0" t="n">
+        <v>180083</v>
+      </c>
+      <c r="C386" s="0" t="n">
+        <v>1011</v>
+      </c>
+      <c r="D386" s="0" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="B387" s="0" t="n">
+        <v>180091</v>
+      </c>
+      <c r="C387" s="0" t="n">
+        <v>3003</v>
+      </c>
+      <c r="D387" s="0" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="B388" s="0" t="n">
+        <v>180092</v>
+      </c>
+      <c r="C388" s="0" t="n">
+        <v>1011</v>
+      </c>
+      <c r="D388" s="0" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="B389" s="0" t="n">
+        <v>180093</v>
+      </c>
+      <c r="C389" s="0" t="n">
+        <v>1001</v>
+      </c>
+      <c r="D389" s="0" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="B390" s="0" t="n">
+        <v>180101</v>
+      </c>
+      <c r="C390" s="0" t="n">
+        <v>2002</v>
+      </c>
+      <c r="D390" s="0" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="B391" s="0" t="n">
+        <v>180102</v>
+      </c>
+      <c r="C391" s="0" t="n">
+        <v>3003</v>
+      </c>
+      <c r="D391" s="0" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="B392" s="0" t="n">
+        <v>180103</v>
+      </c>
+      <c r="C392" s="0" t="n">
+        <v>1002</v>
+      </c>
+      <c r="D392" s="0" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="B393" s="0" t="n">
+        <v>190011</v>
+      </c>
+      <c r="C393" s="0" t="n">
+        <v>1005</v>
+      </c>
+      <c r="D393" s="0" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="B394" s="0" t="n">
+        <v>190021</v>
+      </c>
+      <c r="C394" s="0" t="n">
+        <v>1006</v>
+      </c>
+      <c r="D394" s="0" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="B395" s="0" t="n">
+        <v>190031</v>
+      </c>
+      <c r="C395" s="0" t="n">
+        <v>1007</v>
+      </c>
+      <c r="D395" s="0" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="B396" s="0" t="n">
+        <v>190041</v>
+      </c>
+      <c r="C396" s="0" t="n">
+        <v>1008</v>
+      </c>
+      <c r="D396" s="0" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="B397" s="0" t="n">
+        <v>190042</v>
+      </c>
+      <c r="C397" s="0" t="n">
+        <v>3004</v>
+      </c>
+      <c r="D397" s="0" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="B398" s="0" t="n">
+        <v>190051</v>
+      </c>
+      <c r="C398" s="0" t="n">
+        <v>1009</v>
+      </c>
+      <c r="D398" s="0" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="B399" s="0" t="n">
+        <v>190052</v>
+      </c>
+      <c r="C399" s="0" t="n">
+        <v>3004</v>
+      </c>
+      <c r="D399" s="0" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="B400" s="0" t="n">
+        <v>190061</v>
+      </c>
+      <c r="C400" s="0" t="n">
+        <v>1010</v>
+      </c>
+      <c r="D400" s="0" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="B401" s="0" t="n">
+        <v>190062</v>
+      </c>
+      <c r="C401" s="0" t="n">
+        <v>3004</v>
+      </c>
+      <c r="D401" s="0" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="B402" s="0" t="n">
+        <v>190071</v>
+      </c>
+      <c r="C402" s="0" t="n">
+        <v>3004</v>
+      </c>
+      <c r="D402" s="0" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="B403" s="0" t="n">
+        <v>190072</v>
+      </c>
+      <c r="C403" s="0" t="n">
+        <v>1001</v>
+      </c>
+      <c r="D403" s="0" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="B404" s="0" t="n">
+        <v>190073</v>
+      </c>
+      <c r="C404" s="0" t="n">
+        <v>1002</v>
+      </c>
+      <c r="D404" s="0" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="B405" s="0" t="n">
+        <v>190081</v>
+      </c>
+      <c r="C405" s="0" t="n">
+        <v>3004</v>
+      </c>
+      <c r="D405" s="0" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="B406" s="0" t="n">
+        <v>190082</v>
+      </c>
+      <c r="C406" s="0" t="n">
+        <v>1002</v>
+      </c>
+      <c r="D406" s="0" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="B407" s="0" t="n">
+        <v>190083</v>
+      </c>
+      <c r="C407" s="0" t="n">
+        <v>1003</v>
+      </c>
+      <c r="D407" s="0" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="B408" s="0" t="n">
+        <v>190091</v>
+      </c>
+      <c r="C408" s="0" t="n">
+        <v>3004</v>
+      </c>
+      <c r="D408" s="0" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="B409" s="0" t="n">
+        <v>190092</v>
+      </c>
+      <c r="C409" s="0" t="n">
+        <v>1003</v>
+      </c>
+      <c r="D409" s="0" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="B410" s="0" t="n">
+        <v>190093</v>
+      </c>
+      <c r="C410" s="0" t="n">
+        <v>1004</v>
+      </c>
+      <c r="D410" s="0" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="B411" s="0" t="n">
+        <v>190101</v>
+      </c>
+      <c r="C411" s="0" t="n">
+        <v>2003</v>
+      </c>
+      <c r="D411" s="0" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="B412" s="0" t="n">
+        <v>190102</v>
+      </c>
+      <c r="C412" s="0" t="n">
+        <v>3004</v>
+      </c>
+      <c r="D412" s="0" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="B413" s="0" t="n">
+        <v>190103</v>
+      </c>
+      <c r="C413" s="0" t="n">
+        <v>1005</v>
+      </c>
+      <c r="D413" s="0" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="B414" s="0" t="n">
+        <v>200011</v>
+      </c>
+      <c r="C414" s="0" t="n">
+        <v>1008</v>
+      </c>
+      <c r="D414" s="0" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="B415" s="0" t="n">
+        <v>200021</v>
+      </c>
+      <c r="C415" s="0" t="n">
+        <v>1009</v>
+      </c>
+      <c r="D415" s="0" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="B416" s="0" t="n">
+        <v>200031</v>
+      </c>
+      <c r="C416" s="0" t="n">
+        <v>1010</v>
+      </c>
+      <c r="D416" s="0" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="B417" s="0" t="n">
+        <v>200041</v>
+      </c>
+      <c r="C417" s="0" t="n">
+        <v>1011</v>
+      </c>
+      <c r="D417" s="0" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="B418" s="0" t="n">
+        <v>200042</v>
+      </c>
+      <c r="C418" s="0" t="n">
+        <v>3005</v>
+      </c>
+      <c r="D418" s="0" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="B419" s="0" t="n">
+        <v>200051</v>
+      </c>
+      <c r="C419" s="0" t="n">
+        <v>1001</v>
+      </c>
+      <c r="D419" s="0" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="B420" s="0" t="n">
+        <v>200052</v>
+      </c>
+      <c r="C420" s="0" t="n">
+        <v>3005</v>
+      </c>
+      <c r="D420" s="0" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="B421" s="0" t="n">
+        <v>200061</v>
+      </c>
+      <c r="C421" s="0" t="n">
+        <v>1002</v>
+      </c>
+      <c r="D421" s="0" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="B422" s="0" t="n">
+        <v>200062</v>
+      </c>
+      <c r="C422" s="0" t="n">
+        <v>3005</v>
+      </c>
+      <c r="D422" s="0" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="B423" s="0" t="n">
+        <v>200071</v>
+      </c>
+      <c r="C423" s="0" t="n">
+        <v>3005</v>
+      </c>
+      <c r="D423" s="0" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="B424" s="0" t="n">
+        <v>200072</v>
+      </c>
+      <c r="C424" s="0" t="n">
+        <v>1004</v>
+      </c>
+      <c r="D424" s="0" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="B425" s="0" t="n">
+        <v>200073</v>
+      </c>
+      <c r="C425" s="0" t="n">
+        <v>1005</v>
+      </c>
+      <c r="D425" s="0" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="B426" s="0" t="n">
+        <v>200081</v>
+      </c>
+      <c r="C426" s="0" t="n">
+        <v>3005</v>
+      </c>
+      <c r="D426" s="0" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="B427" s="0" t="n">
+        <v>200082</v>
+      </c>
+      <c r="C427" s="0" t="n">
+        <v>1005</v>
+      </c>
+      <c r="D427" s="0" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="B428" s="0" t="n">
+        <v>200083</v>
+      </c>
+      <c r="C428" s="0" t="n">
+        <v>1006</v>
+      </c>
+      <c r="D428" s="0" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="B429" s="0" t="n">
+        <v>200091</v>
+      </c>
+      <c r="C429" s="0" t="n">
+        <v>3005</v>
+      </c>
+      <c r="D429" s="0" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="B430" s="0" t="n">
+        <v>200092</v>
+      </c>
+      <c r="C430" s="0" t="n">
+        <v>1006</v>
+      </c>
+      <c r="D430" s="0" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="B431" s="0" t="n">
+        <v>200093</v>
+      </c>
+      <c r="C431" s="0" t="n">
+        <v>1007</v>
+      </c>
+      <c r="D431" s="0" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="B432" s="0" t="n">
+        <v>200101</v>
+      </c>
+      <c r="C432" s="0" t="n">
+        <v>2004</v>
+      </c>
+      <c r="D432" s="0" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="B433" s="0" t="n">
+        <v>200102</v>
+      </c>
+      <c r="C433" s="0" t="n">
+        <v>3005</v>
+      </c>
+      <c r="D433" s="0" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="B434" s="0" t="n">
+        <v>200103</v>
+      </c>
+      <c r="C434" s="0" t="n">
+        <v>1008</v>
+      </c>
+      <c r="D434" s="0" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="B435" s="0" t="n">
+        <v>210011</v>
+      </c>
+      <c r="C435" s="0" t="n">
+        <v>1011</v>
+      </c>
+      <c r="D435" s="0" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="B436" s="0" t="n">
+        <v>210021</v>
+      </c>
+      <c r="C436" s="0" t="n">
+        <v>1001</v>
+      </c>
+      <c r="D436" s="0" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="B437" s="0" t="n">
+        <v>210031</v>
+      </c>
+      <c r="C437" s="0" t="n">
+        <v>1002</v>
+      </c>
+      <c r="D437" s="0" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="B438" s="0" t="n">
+        <v>210041</v>
+      </c>
+      <c r="C438" s="0" t="n">
+        <v>1003</v>
+      </c>
+      <c r="D438" s="0" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="B439" s="0" t="n">
+        <v>210042</v>
+      </c>
+      <c r="C439" s="0" t="n">
+        <v>3006</v>
+      </c>
+      <c r="D439" s="0" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="B440" s="0" t="n">
+        <v>210051</v>
+      </c>
+      <c r="C440" s="0" t="n">
+        <v>1004</v>
+      </c>
+      <c r="D440" s="0" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="B441" s="0" t="n">
+        <v>210052</v>
+      </c>
+      <c r="C441" s="0" t="n">
+        <v>3006</v>
+      </c>
+      <c r="D441" s="0" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="B442" s="0" t="n">
+        <v>210061</v>
+      </c>
+      <c r="C442" s="0" t="n">
+        <v>1005</v>
+      </c>
+      <c r="D442" s="0" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="B443" s="0" t="n">
+        <v>210062</v>
+      </c>
+      <c r="C443" s="0" t="n">
+        <v>3006</v>
+      </c>
+      <c r="D443" s="0" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="B444" s="0" t="n">
+        <v>210071</v>
+      </c>
+      <c r="C444" s="0" t="n">
+        <v>3006</v>
+      </c>
+      <c r="D444" s="0" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="B445" s="0" t="n">
+        <v>210072</v>
+      </c>
+      <c r="C445" s="0" t="n">
+        <v>1007</v>
+      </c>
+      <c r="D445" s="0" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="B446" s="0" t="n">
+        <v>210073</v>
+      </c>
+      <c r="C446" s="0" t="n">
+        <v>1008</v>
+      </c>
+      <c r="D446" s="0" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="B447" s="0" t="n">
+        <v>210081</v>
+      </c>
+      <c r="C447" s="0" t="n">
+        <v>3006</v>
+      </c>
+      <c r="D447" s="0" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="B448" s="0" t="n">
+        <v>210082</v>
+      </c>
+      <c r="C448" s="0" t="n">
+        <v>1008</v>
+      </c>
+      <c r="D448" s="0" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="B449" s="0" t="n">
+        <v>210083</v>
+      </c>
+      <c r="C449" s="0" t="n">
+        <v>1009</v>
+      </c>
+      <c r="D449" s="0" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="B450" s="0" t="n">
+        <v>210091</v>
+      </c>
+      <c r="C450" s="0" t="n">
+        <v>3006</v>
+      </c>
+      <c r="D450" s="0" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="B451" s="0" t="n">
+        <v>210092</v>
+      </c>
+      <c r="C451" s="0" t="n">
+        <v>1009</v>
+      </c>
+      <c r="D451" s="0" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="B452" s="0" t="n">
+        <v>210093</v>
+      </c>
+      <c r="C452" s="0" t="n">
+        <v>1010</v>
+      </c>
+      <c r="D452" s="0" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="B453" s="0" t="n">
+        <v>210101</v>
+      </c>
+      <c r="C453" s="0" t="n">
+        <v>2005</v>
+      </c>
+      <c r="D453" s="0" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="B454" s="0" t="n">
+        <v>210102</v>
+      </c>
+      <c r="C454" s="0" t="n">
+        <v>3006</v>
+      </c>
+      <c r="D454" s="0" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="B455" s="0" t="n">
+        <v>210103</v>
+      </c>
+      <c r="C455" s="0" t="n">
+        <v>1011</v>
+      </c>
+      <c r="D455" s="0" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="B456" s="0" t="n">
+        <v>220011</v>
+      </c>
+      <c r="C456" s="0" t="n">
+        <v>1003</v>
+      </c>
+      <c r="D456" s="0" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="B457" s="0" t="n">
+        <v>220021</v>
+      </c>
+      <c r="C457" s="0" t="n">
+        <v>1004</v>
+      </c>
+      <c r="D457" s="0" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="B458" s="0" t="n">
+        <v>220031</v>
+      </c>
+      <c r="C458" s="0" t="n">
+        <v>1005</v>
+      </c>
+      <c r="D458" s="0" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="B459" s="0" t="n">
+        <v>220041</v>
+      </c>
+      <c r="C459" s="0" t="n">
+        <v>1006</v>
+      </c>
+      <c r="D459" s="0" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="B460" s="0" t="n">
+        <v>220042</v>
+      </c>
+      <c r="C460" s="0" t="n">
+        <v>3007</v>
+      </c>
+      <c r="D460" s="0" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="B461" s="0" t="n">
+        <v>220051</v>
+      </c>
+      <c r="C461" s="0" t="n">
+        <v>1007</v>
+      </c>
+      <c r="D461" s="0" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="B462" s="0" t="n">
+        <v>220052</v>
+      </c>
+      <c r="C462" s="0" t="n">
+        <v>3007</v>
+      </c>
+      <c r="D462" s="0" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="B463" s="0" t="n">
+        <v>220061</v>
+      </c>
+      <c r="C463" s="0" t="n">
+        <v>1008</v>
+      </c>
+      <c r="D463" s="0" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="B464" s="0" t="n">
+        <v>220062</v>
+      </c>
+      <c r="C464" s="0" t="n">
+        <v>3007</v>
+      </c>
+      <c r="D464" s="0" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="B465" s="0" t="n">
+        <v>220071</v>
+      </c>
+      <c r="C465" s="0" t="n">
+        <v>3007</v>
+      </c>
+      <c r="D465" s="0" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="B466" s="0" t="n">
+        <v>220072</v>
+      </c>
+      <c r="C466" s="0" t="n">
+        <v>1010</v>
+      </c>
+      <c r="D466" s="0" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="B467" s="0" t="n">
+        <v>220073</v>
+      </c>
+      <c r="C467" s="0" t="n">
+        <v>1011</v>
+      </c>
+      <c r="D467" s="0" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="B468" s="0" t="n">
+        <v>220081</v>
+      </c>
+      <c r="C468" s="0" t="n">
+        <v>3007</v>
+      </c>
+      <c r="D468" s="0" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="B469" s="0" t="n">
+        <v>220082</v>
+      </c>
+      <c r="C469" s="0" t="n">
+        <v>1011</v>
+      </c>
+      <c r="D469" s="0" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="B470" s="0" t="n">
+        <v>220083</v>
+      </c>
+      <c r="C470" s="0" t="n">
+        <v>1001</v>
+      </c>
+      <c r="D470" s="0" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="B471" s="0" t="n">
+        <v>220091</v>
+      </c>
+      <c r="C471" s="0" t="n">
+        <v>3007</v>
+      </c>
+      <c r="D471" s="0" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="B472" s="0" t="n">
+        <v>220092</v>
+      </c>
+      <c r="C472" s="0" t="n">
+        <v>1001</v>
+      </c>
+      <c r="D472" s="0" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="B473" s="0" t="n">
+        <v>220093</v>
+      </c>
+      <c r="C473" s="0" t="n">
+        <v>1002</v>
+      </c>
+      <c r="D473" s="0" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="B474" s="0" t="n">
+        <v>220101</v>
+      </c>
+      <c r="C474" s="0" t="n">
+        <v>2006</v>
+      </c>
+      <c r="D474" s="0" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="B475" s="0" t="n">
+        <v>220102</v>
+      </c>
+      <c r="C475" s="0" t="n">
+        <v>3007</v>
+      </c>
+      <c r="D475" s="0" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="B476" s="0" t="n">
+        <v>220103</v>
+      </c>
+      <c r="C476" s="0" t="n">
+        <v>1003</v>
+      </c>
+      <c r="D476" s="0" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="B477" s="0" t="n">
+        <v>230011</v>
+      </c>
+      <c r="C477" s="0" t="n">
+        <v>1006</v>
+      </c>
+      <c r="D477" s="0" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="B478" s="0" t="n">
+        <v>230021</v>
+      </c>
+      <c r="C478" s="0" t="n">
+        <v>1007</v>
+      </c>
+      <c r="D478" s="0" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="B479" s="0" t="n">
+        <v>230031</v>
+      </c>
+      <c r="C479" s="0" t="n">
+        <v>1008</v>
+      </c>
+      <c r="D479" s="0" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="B480" s="0" t="n">
+        <v>230041</v>
+      </c>
+      <c r="C480" s="0" t="n">
+        <v>1009</v>
+      </c>
+      <c r="D480" s="0" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="B481" s="0" t="n">
+        <v>230042</v>
+      </c>
+      <c r="C481" s="0" t="n">
+        <v>3008</v>
+      </c>
+      <c r="D481" s="0" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="B482" s="0" t="n">
+        <v>230051</v>
+      </c>
+      <c r="C482" s="0" t="n">
+        <v>1010</v>
+      </c>
+      <c r="D482" s="0" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="B483" s="0" t="n">
+        <v>230052</v>
+      </c>
+      <c r="C483" s="0" t="n">
+        <v>3008</v>
+      </c>
+      <c r="D483" s="0" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="B484" s="0" t="n">
+        <v>230061</v>
+      </c>
+      <c r="C484" s="0" t="n">
+        <v>1011</v>
+      </c>
+      <c r="D484" s="0" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="B485" s="0" t="n">
+        <v>230062</v>
+      </c>
+      <c r="C485" s="0" t="n">
+        <v>3008</v>
+      </c>
+      <c r="D485" s="0" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="B486" s="0" t="n">
+        <v>230071</v>
+      </c>
+      <c r="C486" s="0" t="n">
+        <v>3008</v>
+      </c>
+      <c r="D486" s="0" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="B487" s="0" t="n">
+        <v>230072</v>
+      </c>
+      <c r="C487" s="0" t="n">
+        <v>1002</v>
+      </c>
+      <c r="D487" s="0" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="B488" s="0" t="n">
+        <v>230073</v>
+      </c>
+      <c r="C488" s="0" t="n">
+        <v>1003</v>
+      </c>
+      <c r="D488" s="0" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="B489" s="0" t="n">
+        <v>230081</v>
+      </c>
+      <c r="C489" s="0" t="n">
+        <v>3008</v>
+      </c>
+      <c r="D489" s="0" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="B490" s="0" t="n">
+        <v>230082</v>
+      </c>
+      <c r="C490" s="0" t="n">
+        <v>1003</v>
+      </c>
+      <c r="D490" s="0" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="B491" s="0" t="n">
+        <v>230083</v>
+      </c>
+      <c r="C491" s="0" t="n">
+        <v>1004</v>
+      </c>
+      <c r="D491" s="0" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="B492" s="0" t="n">
+        <v>230091</v>
+      </c>
+      <c r="C492" s="0" t="n">
+        <v>3008</v>
+      </c>
+      <c r="D492" s="0" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="B493" s="0" t="n">
+        <v>230092</v>
+      </c>
+      <c r="C493" s="0" t="n">
+        <v>1004</v>
+      </c>
+      <c r="D493" s="0" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="B494" s="0" t="n">
+        <v>230093</v>
+      </c>
+      <c r="C494" s="0" t="n">
+        <v>1005</v>
+      </c>
+      <c r="D494" s="0" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="B495" s="0" t="n">
+        <v>230101</v>
+      </c>
+      <c r="C495" s="0" t="n">
+        <v>2007</v>
+      </c>
+      <c r="D495" s="0" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="B496" s="0" t="n">
+        <v>230102</v>
+      </c>
+      <c r="C496" s="0" t="n">
+        <v>3008</v>
+      </c>
+      <c r="D496" s="0" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="B497" s="0" t="n">
+        <v>230103</v>
+      </c>
+      <c r="C497" s="0" t="n">
+        <v>1006</v>
+      </c>
+      <c r="D497" s="0" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="B498" s="0" t="n">
+        <v>240011</v>
+      </c>
+      <c r="C498" s="0" t="n">
+        <v>1009</v>
+      </c>
+      <c r="D498" s="0" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="B499" s="0" t="n">
+        <v>240021</v>
+      </c>
+      <c r="C499" s="0" t="n">
+        <v>1010</v>
+      </c>
+      <c r="D499" s="0" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="B500" s="0" t="n">
+        <v>240031</v>
+      </c>
+      <c r="C500" s="0" t="n">
+        <v>1011</v>
+      </c>
+      <c r="D500" s="0" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="B501" s="0" t="n">
+        <v>240041</v>
+      </c>
+      <c r="C501" s="0" t="n">
+        <v>1001</v>
+      </c>
+      <c r="D501" s="0" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="B502" s="0" t="n">
+        <v>240042</v>
+      </c>
+      <c r="C502" s="0" t="n">
+        <v>3001</v>
+      </c>
+      <c r="D502" s="0" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="B503" s="0" t="n">
+        <v>240051</v>
+      </c>
+      <c r="C503" s="0" t="n">
+        <v>1002</v>
+      </c>
+      <c r="D503" s="0" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="B504" s="0" t="n">
+        <v>240052</v>
+      </c>
+      <c r="C504" s="0" t="n">
+        <v>3001</v>
+      </c>
+      <c r="D504" s="0" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="B505" s="0" t="n">
+        <v>240061</v>
+      </c>
+      <c r="C505" s="0" t="n">
+        <v>1003</v>
+      </c>
+      <c r="D505" s="0" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="B506" s="0" t="n">
+        <v>240062</v>
+      </c>
+      <c r="C506" s="0" t="n">
+        <v>3001</v>
+      </c>
+      <c r="D506" s="0" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="B507" s="0" t="n">
+        <v>240071</v>
+      </c>
+      <c r="C507" s="0" t="n">
+        <v>3001</v>
+      </c>
+      <c r="D507" s="0" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="B508" s="0" t="n">
+        <v>240072</v>
+      </c>
+      <c r="C508" s="0" t="n">
+        <v>1005</v>
+      </c>
+      <c r="D508" s="0" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="B509" s="0" t="n">
+        <v>240073</v>
+      </c>
+      <c r="C509" s="0" t="n">
+        <v>1006</v>
+      </c>
+      <c r="D509" s="0" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="B510" s="0" t="n">
+        <v>240081</v>
+      </c>
+      <c r="C510" s="0" t="n">
+        <v>3001</v>
+      </c>
+      <c r="D510" s="0" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="B511" s="0" t="n">
+        <v>240082</v>
+      </c>
+      <c r="C511" s="0" t="n">
+        <v>1006</v>
+      </c>
+      <c r="D511" s="0" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="B512" s="0" t="n">
+        <v>240083</v>
+      </c>
+      <c r="C512" s="0" t="n">
+        <v>1007</v>
+      </c>
+      <c r="D512" s="0" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="B513" s="0" t="n">
+        <v>240091</v>
+      </c>
+      <c r="C513" s="0" t="n">
+        <v>3001</v>
+      </c>
+      <c r="D513" s="0" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="B514" s="0" t="n">
+        <v>240092</v>
+      </c>
+      <c r="C514" s="0" t="n">
+        <v>1007</v>
+      </c>
+      <c r="D514" s="0" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="B515" s="0" t="n">
+        <v>240093</v>
+      </c>
+      <c r="C515" s="0" t="n">
+        <v>1008</v>
+      </c>
+      <c r="D515" s="0" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="B516" s="0" t="n">
+        <v>240101</v>
+      </c>
+      <c r="C516" s="0" t="n">
+        <v>2008</v>
+      </c>
+      <c r="D516" s="0" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="B517" s="0" t="n">
+        <v>240102</v>
+      </c>
+      <c r="C517" s="0" t="n">
+        <v>3001</v>
+      </c>
+      <c r="D517" s="0" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="B518" s="0" t="n">
+        <v>240103</v>
+      </c>
+      <c r="C518" s="0" t="n">
+        <v>1009</v>
+      </c>
+      <c r="D518" s="0" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="B519" s="0" t="n">
+        <v>250011</v>
+      </c>
+      <c r="C519" s="0" t="n">
+        <v>1001</v>
+      </c>
+      <c r="D519" s="0" t="n">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="B520" s="0" t="n">
+        <v>250021</v>
+      </c>
+      <c r="C520" s="0" t="n">
+        <v>1002</v>
+      </c>
+      <c r="D520" s="0" t="n">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="B521" s="0" t="n">
+        <v>250031</v>
+      </c>
+      <c r="C521" s="0" t="n">
+        <v>1003</v>
+      </c>
+      <c r="D521" s="0" t="n">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="B522" s="0" t="n">
+        <v>250041</v>
+      </c>
+      <c r="C522" s="0" t="n">
+        <v>1004</v>
+      </c>
+      <c r="D522" s="0" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="B523" s="0" t="n">
+        <v>250042</v>
+      </c>
+      <c r="C523" s="0" t="n">
+        <v>3002</v>
+      </c>
+      <c r="D523" s="0" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="B524" s="0" t="n">
+        <v>250051</v>
+      </c>
+      <c r="C524" s="0" t="n">
+        <v>1005</v>
+      </c>
+      <c r="D524" s="0" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="B525" s="0" t="n">
+        <v>250052</v>
+      </c>
+      <c r="C525" s="0" t="n">
+        <v>3002</v>
+      </c>
+      <c r="D525" s="0" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="B526" s="0" t="n">
+        <v>250061</v>
+      </c>
+      <c r="C526" s="0" t="n">
+        <v>1006</v>
+      </c>
+      <c r="D526" s="0" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="B527" s="0" t="n">
+        <v>250062</v>
+      </c>
+      <c r="C527" s="0" t="n">
+        <v>3002</v>
+      </c>
+      <c r="D527" s="0" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="B528" s="0" t="n">
+        <v>250071</v>
+      </c>
+      <c r="C528" s="0" t="n">
+        <v>3002</v>
+      </c>
+      <c r="D528" s="0" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="B529" s="0" t="n">
+        <v>250072</v>
+      </c>
+      <c r="C529" s="0" t="n">
+        <v>1008</v>
+      </c>
+      <c r="D529" s="0" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="B530" s="0" t="n">
+        <v>250073</v>
+      </c>
+      <c r="C530" s="0" t="n">
+        <v>1009</v>
+      </c>
+      <c r="D530" s="0" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="B531" s="0" t="n">
+        <v>250081</v>
+      </c>
+      <c r="C531" s="0" t="n">
+        <v>3002</v>
+      </c>
+      <c r="D531" s="0" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="B532" s="0" t="n">
+        <v>250082</v>
+      </c>
+      <c r="C532" s="0" t="n">
+        <v>1009</v>
+      </c>
+      <c r="D532" s="0" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="B533" s="0" t="n">
+        <v>250083</v>
+      </c>
+      <c r="C533" s="0" t="n">
+        <v>1010</v>
+      </c>
+      <c r="D533" s="0" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="B534" s="0" t="n">
+        <v>250091</v>
+      </c>
+      <c r="C534" s="0" t="n">
+        <v>3002</v>
+      </c>
+      <c r="D534" s="0" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="B535" s="0" t="n">
+        <v>250092</v>
+      </c>
+      <c r="C535" s="0" t="n">
+        <v>1010</v>
+      </c>
+      <c r="D535" s="0" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="B536" s="0" t="n">
+        <v>250093</v>
+      </c>
+      <c r="C536" s="0" t="n">
+        <v>1011</v>
+      </c>
+      <c r="D536" s="0" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="B537" s="0" t="n">
+        <v>250101</v>
+      </c>
+      <c r="C537" s="0" t="n">
+        <v>2001</v>
+      </c>
+      <c r="D537" s="0" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="B538" s="0" t="n">
+        <v>250102</v>
+      </c>
+      <c r="C538" s="0" t="n">
+        <v>3002</v>
+      </c>
+      <c r="D538" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="B539" s="0" t="n">
+        <v>250103</v>
+      </c>
+      <c r="C539" s="0" t="n">
+        <v>1001</v>
+      </c>
+      <c r="D539" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="B540" s="0" t="n">
+        <v>260011</v>
+      </c>
+      <c r="C540" s="0" t="n">
+        <v>1004</v>
+      </c>
+      <c r="D540" s="0" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="B541" s="0" t="n">
+        <v>260021</v>
+      </c>
+      <c r="C541" s="0" t="n">
+        <v>1005</v>
+      </c>
+      <c r="D541" s="0" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="B542" s="0" t="n">
+        <v>260031</v>
+      </c>
+      <c r="C542" s="0" t="n">
+        <v>1006</v>
+      </c>
+      <c r="D542" s="0" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="B543" s="0" t="n">
+        <v>260041</v>
+      </c>
+      <c r="C543" s="0" t="n">
+        <v>1007</v>
+      </c>
+      <c r="D543" s="0" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="B544" s="0" t="n">
+        <v>260042</v>
+      </c>
+      <c r="C544" s="0" t="n">
+        <v>3003</v>
+      </c>
+      <c r="D544" s="0" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="B545" s="0" t="n">
+        <v>260051</v>
+      </c>
+      <c r="C545" s="0" t="n">
+        <v>1008</v>
+      </c>
+      <c r="D545" s="0" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="B546" s="0" t="n">
+        <v>260052</v>
+      </c>
+      <c r="C546" s="0" t="n">
+        <v>3003</v>
+      </c>
+      <c r="D546" s="0" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="B547" s="0" t="n">
+        <v>260061</v>
+      </c>
+      <c r="C547" s="0" t="n">
+        <v>1009</v>
+      </c>
+      <c r="D547" s="0" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="B548" s="0" t="n">
+        <v>260062</v>
+      </c>
+      <c r="C548" s="0" t="n">
+        <v>3003</v>
+      </c>
+      <c r="D548" s="0" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="B549" s="0" t="n">
+        <v>260071</v>
+      </c>
+      <c r="C549" s="0" t="n">
+        <v>3003</v>
+      </c>
+      <c r="D549" s="0" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="B550" s="0" t="n">
+        <v>260072</v>
+      </c>
+      <c r="C550" s="0" t="n">
+        <v>1011</v>
+      </c>
+      <c r="D550" s="0" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="B551" s="0" t="n">
+        <v>260073</v>
+      </c>
+      <c r="C551" s="0" t="n">
+        <v>1001</v>
+      </c>
+      <c r="D551" s="0" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="B552" s="0" t="n">
+        <v>260081</v>
+      </c>
+      <c r="C552" s="0" t="n">
+        <v>3003</v>
+      </c>
+      <c r="D552" s="0" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="B553" s="0" t="n">
+        <v>260082</v>
+      </c>
+      <c r="C553" s="0" t="n">
+        <v>1001</v>
+      </c>
+      <c r="D553" s="0" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="B554" s="0" t="n">
+        <v>260083</v>
+      </c>
+      <c r="C554" s="0" t="n">
+        <v>1002</v>
+      </c>
+      <c r="D554" s="0" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="B555" s="0" t="n">
+        <v>260091</v>
+      </c>
+      <c r="C555" s="0" t="n">
+        <v>3003</v>
+      </c>
+      <c r="D555" s="0" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="B556" s="0" t="n">
+        <v>260092</v>
+      </c>
+      <c r="C556" s="0" t="n">
+        <v>1002</v>
+      </c>
+      <c r="D556" s="0" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="B557" s="0" t="n">
+        <v>260093</v>
+      </c>
+      <c r="C557" s="0" t="n">
+        <v>1003</v>
+      </c>
+      <c r="D557" s="0" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="B558" s="0" t="n">
+        <v>260101</v>
+      </c>
+      <c r="C558" s="0" t="n">
+        <v>2002</v>
+      </c>
+      <c r="D558" s="0" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="B559" s="0" t="n">
+        <v>260102</v>
+      </c>
+      <c r="C559" s="0" t="n">
+        <v>3003</v>
+      </c>
+      <c r="D559" s="0" t="n">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="B560" s="0" t="n">
+        <v>260103</v>
+      </c>
+      <c r="C560" s="0" t="n">
+        <v>1004</v>
+      </c>
+      <c r="D560" s="0" t="n">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="B561" s="0" t="n">
+        <v>270011</v>
+      </c>
+      <c r="C561" s="0" t="n">
+        <v>1007</v>
+      </c>
+      <c r="D561" s="0" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="B562" s="0" t="n">
+        <v>270021</v>
+      </c>
+      <c r="C562" s="0" t="n">
+        <v>1008</v>
+      </c>
+      <c r="D562" s="0" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="B563" s="0" t="n">
+        <v>270031</v>
+      </c>
+      <c r="C563" s="0" t="n">
+        <v>1009</v>
+      </c>
+      <c r="D563" s="0" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="B564" s="0" t="n">
+        <v>270041</v>
+      </c>
+      <c r="C564" s="0" t="n">
+        <v>1010</v>
+      </c>
+      <c r="D564" s="0" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="B565" s="0" t="n">
+        <v>270042</v>
+      </c>
+      <c r="C565" s="0" t="n">
+        <v>3004</v>
+      </c>
+      <c r="D565" s="0" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="B566" s="0" t="n">
+        <v>270051</v>
+      </c>
+      <c r="C566" s="0" t="n">
+        <v>1011</v>
+      </c>
+      <c r="D566" s="0" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="B567" s="0" t="n">
+        <v>270052</v>
+      </c>
+      <c r="C567" s="0" t="n">
+        <v>3004</v>
+      </c>
+      <c r="D567" s="0" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="B568" s="0" t="n">
+        <v>270061</v>
+      </c>
+      <c r="C568" s="0" t="n">
+        <v>1001</v>
+      </c>
+      <c r="D568" s="0" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="B569" s="0" t="n">
+        <v>270062</v>
+      </c>
+      <c r="C569" s="0" t="n">
+        <v>3004</v>
+      </c>
+      <c r="D569" s="0" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="B570" s="0" t="n">
+        <v>270071</v>
+      </c>
+      <c r="C570" s="0" t="n">
+        <v>3004</v>
+      </c>
+      <c r="D570" s="0" t="n">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="B571" s="0" t="n">
+        <v>270072</v>
+      </c>
+      <c r="C571" s="0" t="n">
+        <v>1003</v>
+      </c>
+      <c r="D571" s="0" t="n">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="B572" s="0" t="n">
+        <v>270073</v>
+      </c>
+      <c r="C572" s="0" t="n">
+        <v>1004</v>
+      </c>
+      <c r="D572" s="0" t="n">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="B573" s="0" t="n">
+        <v>270081</v>
+      </c>
+      <c r="C573" s="0" t="n">
+        <v>3004</v>
+      </c>
+      <c r="D573" s="0" t="n">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="B574" s="0" t="n">
+        <v>270082</v>
+      </c>
+      <c r="C574" s="0" t="n">
+        <v>1004</v>
+      </c>
+      <c r="D574" s="0" t="n">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="B575" s="0" t="n">
+        <v>270083</v>
+      </c>
+      <c r="C575" s="0" t="n">
+        <v>1005</v>
+      </c>
+      <c r="D575" s="0" t="n">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="B576" s="0" t="n">
+        <v>270091</v>
+      </c>
+      <c r="C576" s="0" t="n">
+        <v>3004</v>
+      </c>
+      <c r="D576" s="0" t="n">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="B577" s="0" t="n">
+        <v>270092</v>
+      </c>
+      <c r="C577" s="0" t="n">
+        <v>1005</v>
+      </c>
+      <c r="D577" s="0" t="n">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="B578" s="0" t="n">
+        <v>270093</v>
+      </c>
+      <c r="C578" s="0" t="n">
+        <v>1006</v>
+      </c>
+      <c r="D578" s="0" t="n">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="B579" s="0" t="n">
+        <v>270101</v>
+      </c>
+      <c r="C579" s="0" t="n">
+        <v>2003</v>
+      </c>
+      <c r="D579" s="0" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="B580" s="0" t="n">
+        <v>270102</v>
+      </c>
+      <c r="C580" s="0" t="n">
+        <v>3004</v>
+      </c>
+      <c r="D580" s="0" t="n">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="B581" s="0" t="n">
+        <v>270103</v>
+      </c>
+      <c r="C581" s="0" t="n">
+        <v>1007</v>
+      </c>
+      <c r="D581" s="0" t="n">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="B582" s="0" t="n">
+        <v>280011</v>
+      </c>
+      <c r="C582" s="0" t="n">
+        <v>1010</v>
+      </c>
+      <c r="D582" s="0" t="n">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="B583" s="0" t="n">
+        <v>280021</v>
+      </c>
+      <c r="C583" s="0" t="n">
+        <v>1011</v>
+      </c>
+      <c r="D583" s="0" t="n">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="B584" s="0" t="n">
+        <v>280031</v>
+      </c>
+      <c r="C584" s="0" t="n">
+        <v>1001</v>
+      </c>
+      <c r="D584" s="0" t="n">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="B585" s="0" t="n">
+        <v>280041</v>
+      </c>
+      <c r="C585" s="0" t="n">
+        <v>1002</v>
+      </c>
+      <c r="D585" s="0" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="B586" s="0" t="n">
+        <v>280042</v>
+      </c>
+      <c r="C586" s="0" t="n">
+        <v>3005</v>
+      </c>
+      <c r="D586" s="0" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="B587" s="0" t="n">
+        <v>280051</v>
+      </c>
+      <c r="C587" s="0" t="n">
+        <v>1003</v>
+      </c>
+      <c r="D587" s="0" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="B588" s="0" t="n">
+        <v>280052</v>
+      </c>
+      <c r="C588" s="0" t="n">
+        <v>3005</v>
+      </c>
+      <c r="D588" s="0" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="B589" s="0" t="n">
+        <v>280061</v>
+      </c>
+      <c r="C589" s="0" t="n">
+        <v>1004</v>
+      </c>
+      <c r="D589" s="0" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="B590" s="0" t="n">
+        <v>280062</v>
+      </c>
+      <c r="C590" s="0" t="n">
+        <v>3005</v>
+      </c>
+      <c r="D590" s="0" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="B591" s="0" t="n">
+        <v>280071</v>
+      </c>
+      <c r="C591" s="0" t="n">
+        <v>3005</v>
+      </c>
+      <c r="D591" s="0" t="n">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="B592" s="0" t="n">
+        <v>280072</v>
+      </c>
+      <c r="C592" s="0" t="n">
+        <v>1006</v>
+      </c>
+      <c r="D592" s="0" t="n">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="B593" s="0" t="n">
+        <v>280073</v>
+      </c>
+      <c r="C593" s="0" t="n">
+        <v>1007</v>
+      </c>
+      <c r="D593" s="0" t="n">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="B594" s="0" t="n">
+        <v>280081</v>
+      </c>
+      <c r="C594" s="0" t="n">
+        <v>3005</v>
+      </c>
+      <c r="D594" s="0" t="n">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="B595" s="0" t="n">
+        <v>280082</v>
+      </c>
+      <c r="C595" s="0" t="n">
+        <v>1007</v>
+      </c>
+      <c r="D595" s="0" t="n">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="B596" s="0" t="n">
+        <v>280083</v>
+      </c>
+      <c r="C596" s="0" t="n">
+        <v>1008</v>
+      </c>
+      <c r="D596" s="0" t="n">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="B597" s="0" t="n">
+        <v>280091</v>
+      </c>
+      <c r="C597" s="0" t="n">
+        <v>3005</v>
+      </c>
+      <c r="D597" s="0" t="n">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="B598" s="0" t="n">
+        <v>280092</v>
+      </c>
+      <c r="C598" s="0" t="n">
+        <v>1008</v>
+      </c>
+      <c r="D598" s="0" t="n">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="B599" s="0" t="n">
+        <v>280093</v>
+      </c>
+      <c r="C599" s="0" t="n">
+        <v>1009</v>
+      </c>
+      <c r="D599" s="0" t="n">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="B600" s="0" t="n">
+        <v>280101</v>
+      </c>
+      <c r="C600" s="0" t="n">
+        <v>2004</v>
+      </c>
+      <c r="D600" s="0" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="B601" s="0" t="n">
+        <v>280102</v>
+      </c>
+      <c r="C601" s="0" t="n">
+        <v>3005</v>
+      </c>
+      <c r="D601" s="0" t="n">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="B602" s="0" t="n">
+        <v>280103</v>
+      </c>
+      <c r="C602" s="0" t="n">
+        <v>1010</v>
+      </c>
+      <c r="D602" s="0" t="n">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="B603" s="0" t="n">
+        <v>290011</v>
+      </c>
+      <c r="C603" s="0" t="n">
+        <v>1002</v>
+      </c>
+      <c r="D603" s="0" t="n">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="B604" s="0" t="n">
+        <v>290021</v>
+      </c>
+      <c r="C604" s="0" t="n">
+        <v>1003</v>
+      </c>
+      <c r="D604" s="0" t="n">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="B605" s="0" t="n">
+        <v>290031</v>
+      </c>
+      <c r="C605" s="0" t="n">
+        <v>1004</v>
+      </c>
+      <c r="D605" s="0" t="n">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="B606" s="0" t="n">
+        <v>290041</v>
+      </c>
+      <c r="C606" s="0" t="n">
+        <v>1005</v>
+      </c>
+      <c r="D606" s="0" t="n">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="B607" s="0" t="n">
+        <v>290042</v>
+      </c>
+      <c r="C607" s="0" t="n">
+        <v>3006</v>
+      </c>
+      <c r="D607" s="0" t="n">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="B608" s="0" t="n">
+        <v>290051</v>
+      </c>
+      <c r="C608" s="0" t="n">
+        <v>1006</v>
+      </c>
+      <c r="D608" s="0" t="n">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="B609" s="0" t="n">
+        <v>290052</v>
+      </c>
+      <c r="C609" s="0" t="n">
+        <v>3006</v>
+      </c>
+      <c r="D609" s="0" t="n">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="B610" s="0" t="n">
+        <v>290061</v>
+      </c>
+      <c r="C610" s="0" t="n">
+        <v>1007</v>
+      </c>
+      <c r="D610" s="0" t="n">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="B611" s="0" t="n">
+        <v>290062</v>
+      </c>
+      <c r="C611" s="0" t="n">
+        <v>3006</v>
+      </c>
+      <c r="D611" s="0" t="n">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="B612" s="0" t="n">
+        <v>290071</v>
+      </c>
+      <c r="C612" s="0" t="n">
+        <v>3006</v>
+      </c>
+      <c r="D612" s="0" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="B613" s="0" t="n">
+        <v>290072</v>
+      </c>
+      <c r="C613" s="0" t="n">
+        <v>1009</v>
+      </c>
+      <c r="D613" s="0" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="B614" s="0" t="n">
+        <v>290073</v>
+      </c>
+      <c r="C614" s="0" t="n">
+        <v>1010</v>
+      </c>
+      <c r="D614" s="0" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="B615" s="0" t="n">
+        <v>290081</v>
+      </c>
+      <c r="C615" s="0" t="n">
+        <v>3006</v>
+      </c>
+      <c r="D615" s="0" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="B616" s="0" t="n">
+        <v>290082</v>
+      </c>
+      <c r="C616" s="0" t="n">
+        <v>1010</v>
+      </c>
+      <c r="D616" s="0" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="B617" s="0" t="n">
+        <v>290083</v>
+      </c>
+      <c r="C617" s="0" t="n">
+        <v>1011</v>
+      </c>
+      <c r="D617" s="0" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="B618" s="0" t="n">
+        <v>290091</v>
+      </c>
+      <c r="C618" s="0" t="n">
+        <v>3006</v>
+      </c>
+      <c r="D618" s="0" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="B619" s="0" t="n">
+        <v>290092</v>
+      </c>
+      <c r="C619" s="0" t="n">
+        <v>1011</v>
+      </c>
+      <c r="D619" s="0" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="B620" s="0" t="n">
+        <v>290093</v>
+      </c>
+      <c r="C620" s="0" t="n">
+        <v>1001</v>
+      </c>
+      <c r="D620" s="0" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="B621" s="0" t="n">
+        <v>290101</v>
+      </c>
+      <c r="C621" s="0" t="n">
+        <v>2005</v>
+      </c>
+      <c r="D621" s="0" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="B622" s="0" t="n">
+        <v>290102</v>
+      </c>
+      <c r="C622" s="0" t="n">
+        <v>3006</v>
+      </c>
+      <c r="D622" s="0" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="B623" s="0" t="n">
+        <v>290103</v>
+      </c>
+      <c r="C623" s="0" t="n">
+        <v>1002</v>
+      </c>
+      <c r="D623" s="0" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="B624" s="0" t="n">
+        <v>300011</v>
+      </c>
+      <c r="C624" s="0" t="n">
+        <v>1005</v>
+      </c>
+      <c r="D624" s="0" t="n">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="B625" s="0" t="n">
+        <v>300021</v>
+      </c>
+      <c r="C625" s="0" t="n">
+        <v>1006</v>
+      </c>
+      <c r="D625" s="0" t="n">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="B626" s="0" t="n">
+        <v>300031</v>
+      </c>
+      <c r="C626" s="0" t="n">
+        <v>1007</v>
+      </c>
+      <c r="D626" s="0" t="n">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="B627" s="0" t="n">
+        <v>300041</v>
+      </c>
+      <c r="C627" s="0" t="n">
+        <v>1008</v>
+      </c>
+      <c r="D627" s="0" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="B628" s="0" t="n">
+        <v>300042</v>
+      </c>
+      <c r="C628" s="0" t="n">
+        <v>3007</v>
+      </c>
+      <c r="D628" s="0" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="B629" s="0" t="n">
+        <v>300051</v>
+      </c>
+      <c r="C629" s="0" t="n">
+        <v>1009</v>
+      </c>
+      <c r="D629" s="0" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="B630" s="0" t="n">
+        <v>300052</v>
+      </c>
+      <c r="C630" s="0" t="n">
+        <v>3007</v>
+      </c>
+      <c r="D630" s="0" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="B631" s="0" t="n">
+        <v>300061</v>
+      </c>
+      <c r="C631" s="0" t="n">
+        <v>1010</v>
+      </c>
+      <c r="D631" s="0" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="B632" s="0" t="n">
+        <v>300062</v>
+      </c>
+      <c r="C632" s="0" t="n">
+        <v>3007</v>
+      </c>
+      <c r="D632" s="0" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="B633" s="0" t="n">
+        <v>300071</v>
+      </c>
+      <c r="C633" s="0" t="n">
+        <v>3007</v>
+      </c>
+      <c r="D633" s="0" t="n">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="B634" s="0" t="n">
+        <v>300072</v>
+      </c>
+      <c r="C634" s="0" t="n">
+        <v>1001</v>
+      </c>
+      <c r="D634" s="0" t="n">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="B635" s="0" t="n">
+        <v>300073</v>
+      </c>
+      <c r="C635" s="0" t="n">
+        <v>1002</v>
+      </c>
+      <c r="D635" s="0" t="n">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="B636" s="0" t="n">
+        <v>300081</v>
+      </c>
+      <c r="C636" s="0" t="n">
+        <v>3007</v>
+      </c>
+      <c r="D636" s="0" t="n">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="B637" s="0" t="n">
+        <v>300082</v>
+      </c>
+      <c r="C637" s="0" t="n">
+        <v>1002</v>
+      </c>
+      <c r="D637" s="0" t="n">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="B638" s="0" t="n">
+        <v>300083</v>
+      </c>
+      <c r="C638" s="0" t="n">
+        <v>1003</v>
+      </c>
+      <c r="D638" s="0" t="n">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="B639" s="0" t="n">
+        <v>300091</v>
+      </c>
+      <c r="C639" s="0" t="n">
+        <v>3007</v>
+      </c>
+      <c r="D639" s="0" t="n">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="B640" s="0" t="n">
+        <v>300092</v>
+      </c>
+      <c r="C640" s="0" t="n">
+        <v>1003</v>
+      </c>
+      <c r="D640" s="0" t="n">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="B641" s="0" t="n">
+        <v>300093</v>
+      </c>
+      <c r="C641" s="0" t="n">
+        <v>1004</v>
+      </c>
+      <c r="D641" s="0" t="n">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="B642" s="0" t="n">
+        <v>300101</v>
+      </c>
+      <c r="C642" s="0" t="n">
+        <v>2006</v>
+      </c>
+      <c r="D642" s="0" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="B643" s="0" t="n">
+        <v>300102</v>
+      </c>
+      <c r="C643" s="0" t="n">
+        <v>3007</v>
+      </c>
+      <c r="D643" s="0" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="B644" s="0" t="n">
+        <v>300103</v>
+      </c>
+      <c r="C644" s="0" t="n">
+        <v>1005</v>
+      </c>
+      <c r="D644" s="0" t="n">
+        <v>120</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/Config/MonsterGroupConfig.xlsx
+++ b/Config/MonsterGroupConfig.xlsx
@@ -1336,7 +1336,7 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>3</v>
@@ -1414,7 +1414,7 @@
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>4</v>
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="D41" s="2" t="n">
         <v>7</v>
@@ -1688,7 +1688,7 @@
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="D47" s="2" t="n">
         <v>8</v>
@@ -1854,7 +1854,7 @@
         <v>30083</v>
       </c>
       <c r="C63" s="2" t="n">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="D63" s="2" t="n">
         <v>11</v>
@@ -1920,7 +1920,7 @@
         <v>30103</v>
       </c>
       <c r="C69" s="2" t="n">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="D69" s="2" t="n">
         <v>12</v>
@@ -2086,7 +2086,7 @@
         <v>40083</v>
       </c>
       <c r="C85" s="2" t="n">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="D85" s="2" t="n">
         <v>15</v>
@@ -2152,7 +2152,7 @@
         <v>40103</v>
       </c>
       <c r="C91" s="2" t="n">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="D91" s="2" t="n">
         <v>16</v>
@@ -2318,7 +2318,7 @@
         <v>50083</v>
       </c>
       <c r="C107" s="2" t="n">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="D107" s="2" t="n">
         <v>19</v>
@@ -2384,7 +2384,7 @@
         <v>50103</v>
       </c>
       <c r="C113" s="2" t="n">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="D113" s="2" t="n">
         <v>20</v>
@@ -2550,7 +2550,7 @@
         <v>60083</v>
       </c>
       <c r="C129" s="2" t="n">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="D129" s="2" t="n">
         <v>23</v>
@@ -2616,7 +2616,7 @@
         <v>60103</v>
       </c>
       <c r="C135" s="2" t="n">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="D135" s="2" t="n">
         <v>24</v>
@@ -2782,7 +2782,7 @@
         <v>70083</v>
       </c>
       <c r="C151" s="2" t="n">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="D151" s="2" t="n">
         <v>27</v>
@@ -2848,7 +2848,7 @@
         <v>70103</v>
       </c>
       <c r="C157" s="2" t="n">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="D157" s="2" t="n">
         <v>28</v>
@@ -3014,7 +3014,7 @@
         <v>80083</v>
       </c>
       <c r="C173" s="2" t="n">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="D173" s="2" t="n">
         <v>31</v>
@@ -3080,7 +3080,7 @@
         <v>80103</v>
       </c>
       <c r="C179" s="2" t="n">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="D179" s="2" t="n">
         <v>32</v>
@@ -3246,7 +3246,7 @@
         <v>90083</v>
       </c>
       <c r="C195" s="2" t="n">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="D195" s="2" t="n">
         <v>35</v>
@@ -3312,7 +3312,7 @@
         <v>90103</v>
       </c>
       <c r="C201" s="2" t="n">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="D201" s="2" t="n">
         <v>36</v>
@@ -3478,7 +3478,7 @@
         <v>100083</v>
       </c>
       <c r="C217" s="2" t="n">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="D217" s="2" t="n">
         <v>39</v>
@@ -3544,7 +3544,7 @@
         <v>100103</v>
       </c>
       <c r="C223" s="2" t="n">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="D223" s="2" t="n">
         <v>40</v>
@@ -3710,7 +3710,7 @@
         <v>110083</v>
       </c>
       <c r="C239" s="2" t="n">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="D239" s="2" t="n">
         <v>43</v>
@@ -3776,7 +3776,7 @@
         <v>110103</v>
       </c>
       <c r="C245" s="2" t="n">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="D245" s="2" t="n">
         <v>44</v>
@@ -3974,7 +3974,7 @@
         <v>120093</v>
       </c>
       <c r="C263" s="0" t="n">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="D263" s="0" t="n">
         <v>47</v>
@@ -4128,7 +4128,7 @@
         <v>130072</v>
       </c>
       <c r="C277" s="0" t="n">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="D277" s="0" t="n">
         <v>51</v>
@@ -4304,7 +4304,7 @@
         <v>140051</v>
       </c>
       <c r="C293" s="0" t="n">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="D293" s="0" t="n">
         <v>54</v>
@@ -4491,7 +4491,7 @@
         <v>150021</v>
       </c>
       <c r="C310" s="0" t="n">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="D310" s="0" t="n">
         <v>57</v>
@@ -4865,7 +4865,7 @@
         <v>160083</v>
       </c>
       <c r="C344" s="0" t="n">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="D344" s="0" t="n">
         <v>63</v>
@@ -4887,7 +4887,7 @@
         <v>160092</v>
       </c>
       <c r="C346" s="0" t="n">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="D346" s="0" t="n">
         <v>63</v>
@@ -5206,7 +5206,7 @@
         <v>180041</v>
       </c>
       <c r="C375" s="0" t="n">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="D375" s="0" t="n">
         <v>70</v>
@@ -5404,7 +5404,7 @@
         <v>190011</v>
       </c>
       <c r="C393" s="0" t="n">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="D393" s="0" t="n">
         <v>73</v>
@@ -5624,7 +5624,7 @@
         <v>190103</v>
       </c>
       <c r="C413" s="0" t="n">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="D413" s="0" t="n">
         <v>76</v>
@@ -5756,7 +5756,7 @@
         <v>200073</v>
       </c>
       <c r="C425" s="0" t="n">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="D425" s="0" t="n">
         <v>79</v>
@@ -5778,7 +5778,7 @@
         <v>200082</v>
       </c>
       <c r="C427" s="0" t="n">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="D427" s="0" t="n">
         <v>79</v>
@@ -5943,7 +5943,7 @@
         <v>210061</v>
       </c>
       <c r="C442" s="0" t="n">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="D442" s="0" t="n">
         <v>82</v>
@@ -6119,7 +6119,7 @@
         <v>220031</v>
       </c>
       <c r="C458" s="0" t="n">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="D458" s="0" t="n">
         <v>85</v>
@@ -6515,7 +6515,7 @@
         <v>230093</v>
       </c>
       <c r="C494" s="0" t="n">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="D494" s="0" t="n">
         <v>91</v>
@@ -6669,7 +6669,7 @@
         <v>240072</v>
       </c>
       <c r="C508" s="0" t="n">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="D508" s="0" t="n">
         <v>95</v>
@@ -6845,7 +6845,7 @@
         <v>250051</v>
       </c>
       <c r="C524" s="0" t="n">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="D524" s="0" t="n">
         <v>98</v>
@@ -7032,7 +7032,7 @@
         <v>260021</v>
       </c>
       <c r="C541" s="0" t="n">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="D541" s="0" t="n">
         <v>101</v>
@@ -7406,7 +7406,7 @@
         <v>270083</v>
       </c>
       <c r="C575" s="0" t="n">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="D575" s="0" t="n">
         <v>107</v>
@@ -7428,7 +7428,7 @@
         <v>270092</v>
       </c>
       <c r="C577" s="0" t="n">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="D577" s="0" t="n">
         <v>107</v>
@@ -7747,7 +7747,7 @@
         <v>290041</v>
       </c>
       <c r="C606" s="0" t="n">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="D606" s="0" t="n">
         <v>114</v>
@@ -7945,7 +7945,7 @@
         <v>300011</v>
       </c>
       <c r="C624" s="0" t="n">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="D624" s="0" t="n">
         <v>117</v>
@@ -8165,7 +8165,7 @@
         <v>300103</v>
       </c>
       <c r="C644" s="0" t="n">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="D644" s="0" t="n">
         <v>120</v>

--- a/Config/MonsterGroupConfig.xlsx
+++ b/Config/MonsterGroupConfig.xlsx
@@ -4458,10 +4458,10 @@
         <v>140102</v>
       </c>
       <c r="C307" s="0" t="n">
-        <v>3007</v>
+        <v>1012</v>
       </c>
       <c r="D307" s="0" t="n">
-        <v>56</v>
+        <v>14</v>
       </c>
     </row>
     <row r="308">
@@ -4469,10 +4469,10 @@
         <v>140103</v>
       </c>
       <c r="C308" s="0" t="n">
-        <v>1001</v>
+        <v>1012</v>
       </c>
       <c r="D308" s="0" t="n">
-        <v>56</v>
+        <v>14</v>
       </c>
     </row>
     <row r="309">
@@ -6306,10 +6306,10 @@
         <v>220102</v>
       </c>
       <c r="C475" s="0" t="n">
-        <v>3007</v>
+        <v>1012</v>
       </c>
       <c r="D475" s="0" t="n">
-        <v>88</v>
+        <v>22</v>
       </c>
     </row>
     <row r="476">
@@ -6317,10 +6317,10 @@
         <v>220103</v>
       </c>
       <c r="C476" s="0" t="n">
-        <v>1003</v>
+        <v>1012</v>
       </c>
       <c r="D476" s="0" t="n">
-        <v>88</v>
+        <v>22</v>
       </c>
     </row>
     <row r="477">
@@ -8154,10 +8154,10 @@
         <v>300102</v>
       </c>
       <c r="C643" s="0" t="n">
-        <v>3007</v>
+        <v>1012</v>
       </c>
       <c r="D643" s="0" t="n">
-        <v>120</v>
+        <v>30</v>
       </c>
     </row>
     <row r="644">
@@ -8165,10 +8165,10 @@
         <v>300103</v>
       </c>
       <c r="C644" s="0" t="n">
-        <v>1001</v>
+        <v>1012</v>
       </c>
       <c r="D644" s="0" t="n">
-        <v>120</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/Config/MonsterGroupConfig.xlsx
+++ b/Config/MonsterGroupConfig.xlsx
@@ -1146,7 +1146,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="B5" s="1" t="inlineStr">
         <is>
@@ -4458,10 +4457,10 @@
         <v>140102</v>
       </c>
       <c r="C307" s="0" t="n">
-        <v>1012</v>
+        <v>3006</v>
       </c>
       <c r="D307" s="0" t="n">
-        <v>14</v>
+        <v>56</v>
       </c>
     </row>
     <row r="308">
@@ -4469,10 +4468,10 @@
         <v>140103</v>
       </c>
       <c r="C308" s="0" t="n">
-        <v>1012</v>
+        <v>1009</v>
       </c>
       <c r="D308" s="0" t="n">
-        <v>14</v>
+        <v>56</v>
       </c>
     </row>
     <row r="309">
@@ -6306,10 +6305,10 @@
         <v>220102</v>
       </c>
       <c r="C475" s="0" t="n">
-        <v>1012</v>
+        <v>3006</v>
       </c>
       <c r="D475" s="0" t="n">
-        <v>22</v>
+        <v>88</v>
       </c>
     </row>
     <row r="476">
@@ -6317,10 +6316,10 @@
         <v>220103</v>
       </c>
       <c r="C476" s="0" t="n">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="D476" s="0" t="n">
-        <v>22</v>
+        <v>88</v>
       </c>
     </row>
     <row r="477">
@@ -8154,10 +8153,10 @@
         <v>300102</v>
       </c>
       <c r="C643" s="0" t="n">
-        <v>1012</v>
+        <v>3006</v>
       </c>
       <c r="D643" s="0" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
     </row>
     <row r="644">
@@ -8165,10 +8164,10 @@
         <v>300103</v>
       </c>
       <c r="C644" s="0" t="n">
-        <v>1012</v>
+        <v>1002</v>
       </c>
       <c r="D644" s="0" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/Config/MonsterGroupConfig.xlsx
+++ b/Config/MonsterGroupConfig.xlsx
@@ -1146,6 +1146,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="B5" s="1" t="inlineStr">
         <is>
@@ -1192,7 +1193,7 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>1004</v>
+        <v>9001</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>1</v>
@@ -1270,10 +1271,10 @@
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>3001</v>
+        <v>9002</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1387,10 +1388,10 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>3001</v>
+        <v>9003</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
